--- a/Book2.xlsx
+++ b/Book2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hyper\Desktop\CITADEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C295A511-B2E8-42BC-B45B-BCDE65CFE166}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C3DD37F-F1CA-4984-862D-B3250A6757E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0C5410CF-1285-4D0A-AD74-0DBA11E850F1}"/>
   </bookViews>
@@ -89,7 +89,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -194,11 +194,11 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="35"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="35"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="35" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="35" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="36"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="16" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="35" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="37">
     <cellStyle name="Hyperlink" xfId="36" builtinId="8"/>
@@ -569,7 +569,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D0424DC-D732-4CEF-9BF2-3F571CFCAE22}">
-  <dimension ref="A1:G351"/>
+  <dimension ref="A1:M351"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="12.88671875" bestFit="1" customWidth="1"/>
@@ -581,7 +581,7 @@
     <col min="13" max="13" width="16.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>2</v>
       </c>
@@ -601,7 +601,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>35431</v>
       </c>
@@ -611,7 +611,7 @@
       <c r="C2">
         <v>5.9004545449999997</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2" s="3">
         <v>30089</v>
       </c>
       <c r="E2" s="3">
@@ -621,7 +621,7 @@
         <v>61.6</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>35462</v>
       </c>
@@ -631,7 +631,7 @@
       <c r="C3">
         <v>5.9850000000000003</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="3">
         <v>29909</v>
       </c>
       <c r="E3" s="3">
@@ -640,8 +640,17 @@
       <c r="F3">
         <v>61.9</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L3" t="s">
+        <v>6</v>
+      </c>
+      <c r="M3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>35490</v>
       </c>
@@ -651,7 +660,7 @@
       <c r="C4">
         <v>5.9650684209999998</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="3">
         <v>30864</v>
       </c>
       <c r="E4" s="3">
@@ -661,7 +670,7 @@
         <v>61.8</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>35521</v>
       </c>
@@ -671,7 +680,7 @@
       <c r="C5">
         <v>5.9618318180000003</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="3">
         <v>31679</v>
       </c>
       <c r="E5" s="3">
@@ -681,7 +690,7 @@
         <v>62.6</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>35551</v>
       </c>
@@ -691,7 +700,7 @@
       <c r="C6">
         <v>6.2153799999999997</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="3">
         <v>31202</v>
       </c>
       <c r="E6" s="3">
@@ -700,8 +709,20 @@
       <c r="F6">
         <v>62.1</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="J6" t="s">
+        <v>2</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="L6" s="1">
+        <v>46054</v>
+      </c>
+      <c r="M6" s="7">
+        <v>46134</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>35582</v>
       </c>
@@ -711,7 +732,7 @@
       <c r="C7">
         <v>6.2226619049999998</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="3">
         <v>32246</v>
       </c>
       <c r="E7" s="3">
@@ -720,8 +741,14 @@
       <c r="F7">
         <v>62.5</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="J7" t="s">
+        <v>7</v>
+      </c>
+      <c r="L7" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>35612</v>
       </c>
@@ -731,7 +758,7 @@
       <c r="C8">
         <v>6.5191739130000004</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="3">
         <v>31995</v>
       </c>
       <c r="E8" s="3">
@@ -740,8 +767,17 @@
       <c r="F8">
         <v>62.8</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="J8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L8" s="1">
+        <v>46023</v>
+      </c>
+      <c r="M8" s="7">
+        <v>46133</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>35643</v>
       </c>
@@ -751,7 +787,7 @@
       <c r="C9">
         <v>6.9488200000000004</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D9" s="3">
         <v>30867</v>
       </c>
       <c r="E9" s="3">
@@ -760,8 +796,20 @@
       <c r="F9">
         <v>62.8</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I9" t="s">
+        <v>10</v>
+      </c>
+      <c r="J9" t="s">
+        <v>11</v>
+      </c>
+      <c r="L9" s="1">
+        <v>46054</v>
+      </c>
+      <c r="M9" s="6">
+        <v>46130</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>35674</v>
       </c>
@@ -771,7 +819,7 @@
       <c r="C10">
         <v>6.977181818</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="3">
         <v>31337</v>
       </c>
       <c r="E10" s="3">
@@ -780,8 +828,17 @@
       <c r="F10">
         <v>63</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I10" t="s">
+        <v>13</v>
+      </c>
+      <c r="J10" t="s">
+        <v>14</v>
+      </c>
+      <c r="L10" s="1">
+        <v>46054</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>35704</v>
       </c>
@@ -791,7 +848,7 @@
       <c r="C11">
         <v>7.1462260869999996</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D11" s="3">
         <v>31867</v>
       </c>
       <c r="E11" s="3">
@@ -801,7 +858,7 @@
         <v>63.4</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>35735</v>
       </c>
@@ -811,7 +868,7 @@
       <c r="C12">
         <v>7.2269100000000002</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D12" s="3">
         <v>31847</v>
       </c>
       <c r="E12" s="3">
@@ -821,7 +878,7 @@
         <v>63.6</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>35765</v>
       </c>
@@ -831,7 +888,7 @@
       <c r="C13">
         <v>7.1378619050000003</v>
       </c>
-      <c r="D13" s="4">
+      <c r="D13" s="3">
         <v>32947</v>
       </c>
       <c r="E13" s="3">
@@ -841,7 +898,7 @@
         <v>64.2</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>35796</v>
       </c>
@@ -851,7 +908,7 @@
       <c r="C14">
         <v>7.2678904759999998</v>
       </c>
-      <c r="D14" s="4">
+      <c r="D14" s="3">
         <v>31552</v>
       </c>
       <c r="E14" s="3">
@@ -861,7 +918,7 @@
         <v>64.099999999999994</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>35827</v>
       </c>
@@ -871,7 +928,7 @@
       <c r="C15">
         <v>7.34063</v>
       </c>
-      <c r="D15" s="4">
+      <c r="D15" s="3">
         <v>33016</v>
       </c>
       <c r="E15" s="3">
@@ -881,7 +938,7 @@
         <v>64.400000000000006</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>35855</v>
       </c>
@@ -891,7 +948,7 @@
       <c r="C16">
         <v>7.403313636</v>
       </c>
-      <c r="D16" s="4">
+      <c r="D16" s="3">
         <v>34147</v>
       </c>
       <c r="E16" s="3">
@@ -911,7 +968,7 @@
       <c r="C17">
         <v>7.2518500000000001</v>
       </c>
-      <c r="D17" s="4">
+      <c r="D17" s="3">
         <v>33074</v>
       </c>
       <c r="E17" s="3">
@@ -931,7 +988,7 @@
       <c r="C18">
         <v>7.2595631579999997</v>
       </c>
-      <c r="D18" s="4">
+      <c r="D18" s="3">
         <v>33798</v>
       </c>
       <c r="E18" s="3">
@@ -951,7 +1008,7 @@
       <c r="C19">
         <v>7.1409363639999999</v>
       </c>
-      <c r="D19" s="4">
+      <c r="D19" s="3">
         <v>34470</v>
       </c>
       <c r="E19" s="3">
@@ -971,7 +1028,7 @@
       <c r="C20">
         <v>7.3282695650000003</v>
       </c>
-      <c r="D20" s="4">
+      <c r="D20" s="3">
         <v>33903</v>
       </c>
       <c r="E20" s="3">
@@ -991,7 +1048,7 @@
       <c r="C21">
         <v>7.5308999999999999</v>
       </c>
-      <c r="D21" s="4">
+      <c r="D21" s="3">
         <v>33539</v>
       </c>
       <c r="E21" s="3">
@@ -1011,7 +1068,7 @@
       <c r="C22">
         <v>7.2790136360000002</v>
       </c>
-      <c r="D22" s="4">
+      <c r="D22" s="3">
         <v>34300</v>
       </c>
       <c r="E22" s="3">
@@ -1031,7 +1088,7 @@
       <c r="C23">
         <v>7.5534363640000004</v>
       </c>
-      <c r="D23" s="4">
+      <c r="D23" s="3">
         <v>33472</v>
       </c>
       <c r="E23" s="3">
@@ -1051,7 +1108,7 @@
       <c r="C24">
         <v>6.8577476190000004</v>
       </c>
-      <c r="D24" s="4">
+      <c r="D24" s="3">
         <v>33877</v>
       </c>
       <c r="E24" s="3">
@@ -1071,7 +1128,7 @@
       <c r="C25">
         <v>6.3749619050000002</v>
       </c>
-      <c r="D25" s="4">
+      <c r="D25" s="3">
         <v>34137</v>
       </c>
       <c r="E25" s="3">
@@ -1091,7 +1148,7 @@
       <c r="C26">
         <v>5.9922050000000002</v>
       </c>
-      <c r="D26" s="4">
+      <c r="D26" s="3">
         <v>34499</v>
       </c>
       <c r="E26" s="3">
@@ -1111,7 +1168,7 @@
       <c r="C27">
         <v>5.7693349999999999</v>
       </c>
-      <c r="D27" s="4">
+      <c r="D27" s="3">
         <v>34528</v>
       </c>
       <c r="E27" s="3">
@@ -1131,7 +1188,7 @@
       <c r="C28">
         <v>5.5665043479999996</v>
       </c>
-      <c r="D28" s="4">
+      <c r="D28" s="3">
         <v>35866</v>
       </c>
       <c r="E28" s="3">
@@ -1151,7 +1208,7 @@
       <c r="C29">
         <v>5.3294899999999998</v>
       </c>
-      <c r="D29" s="4">
+      <c r="D29" s="3">
         <v>34989</v>
       </c>
       <c r="E29" s="3">
@@ -1171,7 +1228,7 @@
       <c r="C30">
         <v>5.2688842109999996</v>
       </c>
-      <c r="D30" s="4">
+      <c r="D30" s="3">
         <v>35157</v>
       </c>
       <c r="E30" s="3">
@@ -1191,7 +1248,7 @@
       <c r="C31">
         <v>4.897181818</v>
       </c>
-      <c r="D31" s="4">
+      <c r="D31" s="3">
         <v>36272</v>
       </c>
       <c r="E31" s="3">
@@ -1211,7 +1268,7 @@
       <c r="C32">
         <v>4.9970045450000002</v>
       </c>
-      <c r="D32" s="4">
+      <c r="D32" s="3">
         <v>36015</v>
       </c>
       <c r="E32" s="3">
@@ -1231,7 +1288,7 @@
       <c r="C33">
         <v>4.8419285710000004</v>
       </c>
-      <c r="D33" s="4">
+      <c r="D33" s="3">
         <v>37119</v>
       </c>
       <c r="E33" s="3">
@@ -1251,7 +1308,7 @@
       <c r="C34">
         <v>4.9190136359999999</v>
       </c>
-      <c r="D34" s="4">
+      <c r="D34" s="3">
         <v>36722</v>
       </c>
       <c r="E34" s="3">
@@ -1271,7 +1328,7 @@
       <c r="C35">
         <v>5.0623333329999998</v>
       </c>
-      <c r="D35" s="4">
+      <c r="D35" s="3">
         <v>37279</v>
       </c>
       <c r="E35" s="3">
@@ -1291,7 +1348,7 @@
       <c r="C36">
         <v>5.2513409089999996</v>
       </c>
-      <c r="D36" s="4">
+      <c r="D36" s="3">
         <v>37663</v>
       </c>
       <c r="E36" s="3">
@@ -1311,7 +1368,7 @@
       <c r="C37">
         <v>4.7813499999999998</v>
       </c>
-      <c r="D37" s="4">
+      <c r="D37" s="3">
         <v>37183</v>
       </c>
       <c r="E37" s="3">
@@ -1331,7 +1388,7 @@
       <c r="C38">
         <v>5.3526499999999997</v>
       </c>
-      <c r="D38" s="4">
+      <c r="D38" s="3">
         <v>37867</v>
       </c>
       <c r="E38" s="3">
@@ -1351,7 +1408,7 @@
       <c r="C39">
         <v>5.840809524</v>
       </c>
-      <c r="D39" s="4">
+      <c r="D39" s="3">
         <v>37582</v>
       </c>
       <c r="E39" s="3">
@@ -1371,7 +1428,7 @@
       <c r="C40">
         <v>5.7620043479999996</v>
       </c>
-      <c r="D40" s="4">
+      <c r="D40" s="3">
         <v>37852</v>
       </c>
       <c r="E40" s="3">
@@ -1391,7 +1448,7 @@
       <c r="C41">
         <v>5.9347333329999996</v>
       </c>
-      <c r="D41" s="4">
+      <c r="D41" s="3">
         <v>38938</v>
       </c>
       <c r="E41" s="3">
@@ -1411,7 +1468,7 @@
       <c r="C42">
         <v>5.912204762</v>
       </c>
-      <c r="D42" s="4">
+      <c r="D42" s="3">
         <v>38629</v>
       </c>
       <c r="E42" s="3">
@@ -1431,7 +1488,7 @@
       <c r="C43">
         <v>5.9031727270000003</v>
       </c>
-      <c r="D43" s="4">
+      <c r="D43" s="3">
         <v>39331</v>
       </c>
       <c r="E43" s="3">
@@ -1451,7 +1508,7 @@
       <c r="C44">
         <v>5.9867047619999996</v>
       </c>
-      <c r="D44" s="4">
+      <c r="D44" s="3">
         <v>40284</v>
       </c>
       <c r="E44" s="3">
@@ -1471,7 +1528,7 @@
       <c r="C45">
         <v>5.884622727</v>
       </c>
-      <c r="D45" s="4">
+      <c r="D45" s="3">
         <v>39660</v>
       </c>
       <c r="E45" s="3">
@@ -1491,7 +1548,7 @@
       <c r="C46">
         <v>6.1258809520000002</v>
       </c>
-      <c r="D46" s="4">
+      <c r="D46" s="3">
         <v>39346</v>
       </c>
       <c r="E46" s="3">
@@ -1511,7 +1568,7 @@
       <c r="C47">
         <v>5.8135000000000003</v>
       </c>
-      <c r="D47" s="4">
+      <c r="D47" s="3">
         <v>39927</v>
       </c>
       <c r="E47" s="3">
@@ -1531,7 +1588,7 @@
       <c r="C48">
         <v>5.9811136359999999</v>
       </c>
-      <c r="D48" s="4">
+      <c r="D48" s="3">
         <v>41707</v>
       </c>
       <c r="E48" s="3">
@@ -1551,7 +1608,7 @@
       <c r="C49">
         <v>5.7383421050000001</v>
       </c>
-      <c r="D49" s="4">
+      <c r="D49" s="3">
         <v>41673</v>
       </c>
       <c r="E49" s="3">
@@ -1571,7 +1628,7 @@
       <c r="C50">
         <v>5.9208136360000001</v>
       </c>
-      <c r="D50" s="4">
+      <c r="D50" s="3">
         <v>41948</v>
       </c>
       <c r="E50" s="3">
@@ -1591,7 +1648,7 @@
       <c r="C51">
         <v>5.8446699999999998</v>
       </c>
-      <c r="D51" s="4">
+      <c r="D51" s="3">
         <v>41915</v>
       </c>
       <c r="E51" s="3">
@@ -1611,7 +1668,7 @@
       <c r="C52">
         <v>5.4016863639999997</v>
       </c>
-      <c r="D52" s="4">
+      <c r="D52" s="3">
         <v>42079</v>
       </c>
       <c r="E52" s="3">
@@ -1620,7 +1677,7 @@
       <c r="F52">
         <v>71.400000000000006</v>
       </c>
-      <c r="G52" s="5">
+      <c r="G52" s="4">
         <v>6.1</v>
       </c>
     </row>
@@ -1634,7 +1691,7 @@
       <c r="C53">
         <v>5.3159157889999999</v>
       </c>
-      <c r="D53" s="4">
+      <c r="D53" s="3">
         <v>41793</v>
       </c>
       <c r="E53" s="3">
@@ -1643,7 +1700,7 @@
       <c r="F53">
         <v>71.2</v>
       </c>
-      <c r="G53" s="5">
+      <c r="G53" s="4">
         <v>6.2</v>
       </c>
     </row>
@@ -1657,7 +1714,7 @@
       <c r="C54">
         <v>5.5202666669999996</v>
       </c>
-      <c r="D54" s="4">
+      <c r="D54" s="3">
         <v>41860</v>
       </c>
       <c r="E54" s="3">
@@ -1666,7 +1723,7 @@
       <c r="F54">
         <v>71.3</v>
       </c>
-      <c r="G54" s="5">
+      <c r="G54" s="4">
         <v>5.0999999999999996</v>
       </c>
     </row>
@@ -1680,7 +1737,7 @@
       <c r="C55">
         <v>4.7796190479999998</v>
       </c>
-      <c r="D55" s="4">
+      <c r="D55" s="3">
         <v>43149</v>
       </c>
       <c r="E55" s="3">
@@ -1689,7 +1746,7 @@
       <c r="F55">
         <v>71.599999999999994</v>
       </c>
-      <c r="G55" s="5">
+      <c r="G55" s="4">
         <v>5.5</v>
       </c>
     </row>
@@ -1703,7 +1760,7 @@
       <c r="C56">
         <v>5.2942636360000002</v>
       </c>
-      <c r="D56" s="4">
+      <c r="D56" s="3">
         <v>41547</v>
       </c>
       <c r="E56" s="3">
@@ -1712,7 +1769,7 @@
       <c r="F56">
         <v>71.599999999999994</v>
       </c>
-      <c r="G56" s="5">
+      <c r="G56" s="4">
         <v>5.2</v>
       </c>
     </row>
@@ -1726,7 +1783,7 @@
       <c r="C57">
         <v>4.8046272730000004</v>
       </c>
-      <c r="D57" s="4">
+      <c r="D57" s="3">
         <v>42571</v>
       </c>
       <c r="E57" s="3">
@@ -1735,7 +1792,7 @@
       <c r="F57">
         <v>71.7</v>
       </c>
-      <c r="G57" s="5">
+      <c r="G57" s="4">
         <v>5.3</v>
       </c>
     </row>
@@ -1749,7 +1806,7 @@
       <c r="C58">
         <v>4.8526199999999999</v>
       </c>
-      <c r="D58" s="4">
+      <c r="D58" s="3">
         <v>40542</v>
       </c>
       <c r="E58" s="3">
@@ -1758,7 +1815,7 @@
       <c r="F58">
         <v>71.599999999999994</v>
       </c>
-      <c r="G58" s="5">
+      <c r="G58" s="4">
         <v>4.8</v>
       </c>
     </row>
@@ -1772,7 +1829,7 @@
       <c r="C59">
         <v>4.5973391299999999</v>
       </c>
-      <c r="D59" s="4">
+      <c r="D59" s="3">
         <v>41537</v>
       </c>
       <c r="E59" s="3">
@@ -1781,7 +1838,7 @@
       <c r="F59">
         <v>71.8</v>
       </c>
-      <c r="G59" s="5">
+      <c r="G59" s="4">
         <v>4.8</v>
       </c>
     </row>
@@ -1795,7 +1852,7 @@
       <c r="C60">
         <v>3.5760681820000002</v>
       </c>
-      <c r="D60" s="4">
+      <c r="D60" s="3">
         <v>40795</v>
       </c>
       <c r="E60" s="3">
@@ -1804,7 +1861,7 @@
       <c r="F60">
         <v>71.8</v>
       </c>
-      <c r="G60" s="5">
+      <c r="G60" s="4">
         <v>4.5999999999999996</v>
       </c>
     </row>
@@ -1818,7 +1875,7 @@
       <c r="C61">
         <v>4.5840842110000004</v>
       </c>
-      <c r="D61" s="4">
+      <c r="D61" s="3">
         <v>41141</v>
       </c>
       <c r="E61" s="3">
@@ -1827,7 +1884,7 @@
       <c r="F61">
         <v>71.8</v>
       </c>
-      <c r="G61" s="5">
+      <c r="G61" s="4">
         <v>4.2</v>
       </c>
     </row>
@@ -1841,7 +1898,7 @@
       <c r="C62">
         <v>3.7684818180000001</v>
       </c>
-      <c r="D62" s="4">
+      <c r="D62" s="3">
         <v>41651</v>
       </c>
       <c r="E62" s="3">
@@ -1850,7 +1907,7 @@
       <c r="F62">
         <v>72</v>
       </c>
-      <c r="G62" s="5">
+      <c r="G62" s="4">
         <v>3.8</v>
       </c>
     </row>
@@ -1864,7 +1921,7 @@
       <c r="C63">
         <v>4.0573550000000003</v>
       </c>
-      <c r="D63" s="4">
+      <c r="D63" s="3">
         <v>42813</v>
       </c>
       <c r="E63" s="3">
@@ -1873,7 +1930,7 @@
       <c r="F63">
         <v>71.8</v>
       </c>
-      <c r="G63" s="5">
+      <c r="G63" s="4">
         <v>3.2</v>
       </c>
     </row>
@@ -1887,7 +1944,7 @@
       <c r="C64">
         <v>4.043145</v>
       </c>
-      <c r="D64" s="4">
+      <c r="D64" s="3">
         <v>43396</v>
       </c>
       <c r="E64" s="3">
@@ -1896,7 +1953,7 @@
       <c r="F64">
         <v>72</v>
       </c>
-      <c r="G64" s="5">
+      <c r="G64" s="4">
         <v>3</v>
       </c>
     </row>
@@ -1910,7 +1967,7 @@
       <c r="C65">
         <v>3.7519571429999998</v>
       </c>
-      <c r="D65" s="4">
+      <c r="D65" s="3">
         <v>44354</v>
       </c>
       <c r="E65" s="3">
@@ -1919,7 +1976,7 @@
       <c r="F65">
         <v>72.599999999999994</v>
       </c>
-      <c r="G65" s="5">
+      <c r="G65" s="4">
         <v>3</v>
       </c>
     </row>
@@ -1933,7 +1990,7 @@
       <c r="C66">
         <v>3.927286364</v>
       </c>
-      <c r="D66" s="4">
+      <c r="D66" s="3">
         <v>44935</v>
       </c>
       <c r="E66" s="3">
@@ -1942,7 +1999,7 @@
       <c r="F66">
         <v>72.900000000000006</v>
       </c>
-      <c r="G66" s="5">
+      <c r="G66" s="4">
         <v>3.3</v>
       </c>
     </row>
@@ -1956,7 +2013,7 @@
       <c r="C67">
         <v>3.5005777779999998</v>
       </c>
-      <c r="D67" s="4">
+      <c r="D67" s="3">
         <v>43486</v>
       </c>
       <c r="E67" s="3">
@@ -1965,7 +2022,7 @@
       <c r="F67">
         <v>71.2</v>
       </c>
-      <c r="G67" s="5">
+      <c r="G67" s="4">
         <v>3.7</v>
       </c>
     </row>
@@ -1979,7 +2036,7 @@
       <c r="C68">
         <v>3.8610130429999998</v>
       </c>
-      <c r="D68" s="4">
+      <c r="D68" s="3">
         <v>44955</v>
       </c>
       <c r="E68" s="3">
@@ -1988,7 +2045,7 @@
       <c r="F68">
         <v>72.5</v>
       </c>
-      <c r="G68" s="5">
+      <c r="G68" s="4">
         <v>3.8</v>
       </c>
     </row>
@@ -2002,7 +2059,7 @@
       <c r="C69">
         <v>4.1371190479999997</v>
       </c>
-      <c r="D69" s="4">
+      <c r="D69" s="3">
         <v>42763</v>
       </c>
       <c r="E69" s="3">
@@ -2011,7 +2068,7 @@
       <c r="F69">
         <v>72.8</v>
       </c>
-      <c r="G69" s="5">
+      <c r="G69" s="4">
         <v>3.6</v>
       </c>
     </row>
@@ -2025,7 +2082,7 @@
       <c r="C70">
         <v>3.8711142860000001</v>
       </c>
-      <c r="D70" s="4">
+      <c r="D70" s="3">
         <v>43361</v>
       </c>
       <c r="E70" s="3">
@@ -2034,7 +2091,7 @@
       <c r="F70">
         <v>73.099999999999994</v>
       </c>
-      <c r="G70" s="5">
+      <c r="G70" s="4">
         <v>3.4</v>
       </c>
     </row>
@@ -2048,7 +2105,7 @@
       <c r="C71">
         <v>4.0884260870000002</v>
       </c>
-      <c r="D71" s="4">
+      <c r="D71" s="3">
         <v>44029</v>
       </c>
       <c r="E71" s="3">
@@ -2057,7 +2114,7 @@
       <c r="F71">
         <v>73.099999999999994</v>
       </c>
-      <c r="G71" s="5">
+      <c r="G71" s="4">
         <v>3.1</v>
       </c>
     </row>
@@ -2071,7 +2128,7 @@
       <c r="C72">
         <v>3.6520999999999999</v>
       </c>
-      <c r="D72" s="4">
+      <c r="D72" s="3">
         <v>44162</v>
       </c>
       <c r="E72" s="3">
@@ -2080,7 +2137,7 @@
       <c r="F72">
         <v>73.3</v>
       </c>
-      <c r="G72" s="5">
+      <c r="G72" s="4">
         <v>3</v>
       </c>
     </row>
@@ -2094,7 +2151,7 @@
       <c r="C73">
         <v>4.3952999999999998</v>
       </c>
-      <c r="D73" s="4">
+      <c r="D73" s="3">
         <v>42677</v>
       </c>
       <c r="E73" s="3">
@@ -2103,7 +2160,7 @@
       <c r="F73">
         <v>73.400000000000006</v>
       </c>
-      <c r="G73" s="5">
+      <c r="G73" s="4">
         <v>2.8</v>
       </c>
     </row>
@@ -2117,7 +2174,7 @@
       <c r="C74">
         <v>3.804418182</v>
       </c>
-      <c r="D74" s="4">
+      <c r="D74" s="3">
         <v>44130</v>
       </c>
       <c r="E74" s="3">
@@ -2126,7 +2183,7 @@
       <c r="F74">
         <v>73.7</v>
       </c>
-      <c r="G74" s="5">
+      <c r="G74" s="4">
         <v>2.5</v>
       </c>
     </row>
@@ -2140,7 +2197,7 @@
       <c r="C75">
         <v>3.7242600000000001</v>
       </c>
-      <c r="D75" s="4">
+      <c r="D75" s="3">
         <v>43716</v>
       </c>
       <c r="E75" s="3">
@@ -2149,7 +2206,7 @@
       <c r="F75">
         <v>73.900000000000006</v>
       </c>
-      <c r="G75" s="5">
+      <c r="G75" s="4">
         <v>2.2000000000000002</v>
       </c>
     </row>
@@ -2163,7 +2220,7 @@
       <c r="C76">
         <v>3.9196142859999998</v>
       </c>
-      <c r="D76" s="4">
+      <c r="D76" s="3">
         <v>44327</v>
       </c>
       <c r="E76" s="3">
@@ -2172,7 +2229,7 @@
       <c r="F76">
         <v>73.8</v>
       </c>
-      <c r="G76" s="5">
+      <c r="G76" s="4">
         <v>2.8</v>
       </c>
     </row>
@@ -2186,7 +2243,7 @@
       <c r="C77">
         <v>3.6189749999999998</v>
       </c>
-      <c r="D77" s="4">
+      <c r="D77" s="3">
         <v>43272</v>
       </c>
       <c r="E77" s="3">
@@ -2195,7 +2252,7 @@
       <c r="F77">
         <v>74.400000000000006</v>
       </c>
-      <c r="G77" s="5">
+      <c r="G77" s="4">
         <v>3</v>
       </c>
     </row>
@@ -2209,7 +2266,7 @@
       <c r="C78">
         <v>3.6875100000000001</v>
       </c>
-      <c r="D78" s="4">
+      <c r="D78" s="3">
         <v>43900</v>
       </c>
       <c r="E78" s="3">
@@ -2218,7 +2275,7 @@
       <c r="F78">
         <v>74.3</v>
       </c>
-      <c r="G78" s="5">
+      <c r="G78" s="4">
         <v>3.3</v>
       </c>
     </row>
@@ -2232,7 +2289,7 @@
       <c r="C79">
         <v>3.6535047619999999</v>
       </c>
-      <c r="D79" s="4">
+      <c r="D79" s="3">
         <v>43919</v>
       </c>
       <c r="E79" s="3">
@@ -2241,7 +2298,7 @@
       <c r="F79">
         <v>74.8</v>
       </c>
-      <c r="G79" s="5">
+      <c r="G79" s="4">
         <v>2.7</v>
       </c>
     </row>
@@ -2255,7 +2312,7 @@
       <c r="C80">
         <v>3.2923478259999999</v>
       </c>
-      <c r="D80" s="4">
+      <c r="D80" s="3">
         <v>43977</v>
       </c>
       <c r="E80" s="3">
@@ -2264,7 +2321,7 @@
       <c r="F80">
         <v>75.099999999999994</v>
       </c>
-      <c r="G80" s="5">
+      <c r="G80" s="4">
         <v>2.7</v>
       </c>
     </row>
@@ -2278,7 +2335,7 @@
       <c r="C81">
         <v>3.50528</v>
       </c>
-      <c r="D81" s="4">
+      <c r="D81" s="3">
         <v>43867</v>
       </c>
       <c r="E81" s="3">
@@ -2287,7 +2344,7 @@
       <c r="F81">
         <v>75.099999999999994</v>
       </c>
-      <c r="G81" s="5">
+      <c r="G81" s="4">
         <v>2.9</v>
       </c>
     </row>
@@ -2301,7 +2358,7 @@
       <c r="C82">
         <v>3.5178863640000002</v>
       </c>
-      <c r="D82" s="4">
+      <c r="D82" s="3">
         <v>44874</v>
       </c>
       <c r="E82" s="3">
@@ -2310,7 +2367,7 @@
       <c r="F82">
         <v>75.5</v>
       </c>
-      <c r="G82" s="5">
+      <c r="G82" s="4">
         <v>3.3</v>
       </c>
     </row>
@@ -2324,7 +2381,7 @@
       <c r="C83">
         <v>3.355004348</v>
       </c>
-      <c r="D83" s="4">
+      <c r="D83" s="3">
         <v>45535</v>
       </c>
       <c r="E83" s="3">
@@ -2333,7 +2390,7 @@
       <c r="F83">
         <v>75.900000000000006</v>
       </c>
-      <c r="G83" s="5">
+      <c r="G83" s="4">
         <v>3.7</v>
       </c>
     </row>
@@ -2347,7 +2404,7 @@
       <c r="C84">
         <v>3.5483449999999999</v>
       </c>
-      <c r="D84" s="4">
+      <c r="D84" s="3">
         <v>45013</v>
       </c>
       <c r="E84" s="3">
@@ -2356,7 +2413,7 @@
       <c r="F84">
         <v>75.7</v>
       </c>
-      <c r="G84" s="5">
+      <c r="G84" s="4">
         <v>3.9</v>
       </c>
     </row>
@@ -2370,7 +2427,7 @@
       <c r="C85">
         <v>3.777752381</v>
       </c>
-      <c r="D85" s="4">
+      <c r="D85" s="3">
         <v>46128</v>
       </c>
       <c r="E85" s="3">
@@ -2379,7 +2436,7 @@
       <c r="F85">
         <v>76</v>
       </c>
-      <c r="G85" s="5">
+      <c r="G85" s="4">
         <v>4.0999999999999996</v>
       </c>
     </row>
@@ -2393,7 +2450,7 @@
       <c r="C86">
         <v>3.715857143</v>
       </c>
-      <c r="D86" s="4">
+      <c r="D86" s="3">
         <v>45843</v>
       </c>
       <c r="E86" s="3">
@@ -2402,7 +2459,7 @@
       <c r="F86">
         <v>75.900000000000006</v>
       </c>
-      <c r="G86" s="5">
+      <c r="G86" s="4">
         <v>5.0999999999999996</v>
       </c>
     </row>
@@ -2416,7 +2473,7 @@
       <c r="C87">
         <v>4.0873200000000001</v>
       </c>
-      <c r="D87" s="4">
+      <c r="D87" s="3">
         <v>45625</v>
       </c>
       <c r="E87" s="3">
@@ -2425,7 +2482,7 @@
       <c r="F87">
         <v>76</v>
       </c>
-      <c r="G87" s="5">
+      <c r="G87" s="4">
         <v>4.9000000000000004</v>
       </c>
     </row>
@@ -2439,7 +2496,7 @@
       <c r="C88">
         <v>3.9039782609999998</v>
       </c>
-      <c r="D88" s="4">
+      <c r="D88" s="3">
         <v>46050</v>
       </c>
       <c r="E88" s="3">
@@ -2448,7 +2505,7 @@
       <c r="F88">
         <v>76.099999999999994</v>
       </c>
-      <c r="G88" s="5">
+      <c r="G88" s="4">
         <v>4.7</v>
       </c>
     </row>
@@ -2462,7 +2519,7 @@
       <c r="C89">
         <v>3.8914149999999998</v>
       </c>
-      <c r="D89" s="4">
+      <c r="D89" s="3">
         <v>46792</v>
       </c>
       <c r="E89" s="3">
@@ -2471,7 +2528,7 @@
       <c r="F89">
         <v>76</v>
       </c>
-      <c r="G89" s="5">
+      <c r="G89" s="4">
         <v>3.7</v>
       </c>
     </row>
@@ -2485,7 +2542,7 @@
       <c r="C90">
         <v>4.2029684209999996</v>
       </c>
-      <c r="D90" s="4">
+      <c r="D90" s="3">
         <v>46891</v>
       </c>
       <c r="E90" s="3">
@@ -2494,7 +2551,7 @@
       <c r="F90">
         <v>76.3</v>
       </c>
-      <c r="G90" s="5">
+      <c r="G90" s="4">
         <v>4.0999999999999996</v>
       </c>
     </row>
@@ -2508,7 +2565,7 @@
       <c r="C91">
         <v>4.3627636360000004</v>
       </c>
-      <c r="D91" s="4">
+      <c r="D91" s="3">
         <v>47379</v>
       </c>
       <c r="E91" s="3">
@@ -2517,7 +2574,7 @@
       <c r="F91">
         <v>76.5</v>
       </c>
-      <c r="G91" s="5">
+      <c r="G91" s="4">
         <v>4.2</v>
       </c>
     </row>
@@ -2531,7 +2588,7 @@
       <c r="C92">
         <v>4.46225</v>
       </c>
-      <c r="D92" s="4">
+      <c r="D92" s="3">
         <v>48302</v>
       </c>
       <c r="E92" s="3">
@@ -2540,7 +2597,7 @@
       <c r="F92">
         <v>76.5</v>
       </c>
-      <c r="G92" s="5">
+      <c r="G92" s="4">
         <v>4.0999999999999996</v>
       </c>
     </row>
@@ -2554,7 +2611,7 @@
       <c r="C93">
         <v>4.629985714</v>
       </c>
-      <c r="D93" s="4">
+      <c r="D93" s="3">
         <v>48650</v>
       </c>
       <c r="E93" s="3">
@@ -2563,7 +2620,7 @@
       <c r="F93">
         <v>76.400000000000006</v>
       </c>
-      <c r="G93" s="5">
+      <c r="G93" s="4">
         <v>4.0999999999999996</v>
       </c>
     </row>
@@ -2577,7 +2634,7 @@
       <c r="C94">
         <v>4.7314409089999998</v>
       </c>
-      <c r="D94" s="4">
+      <c r="D94" s="3">
         <v>47842</v>
       </c>
       <c r="E94" s="3">
@@ -2586,7 +2643,7 @@
       <c r="F94">
         <v>76.599999999999994</v>
       </c>
-      <c r="G94" s="5">
+      <c r="G94" s="4">
         <v>4.0999999999999996</v>
       </c>
     </row>
@@ -2600,7 +2657,7 @@
       <c r="C95">
         <v>4.7297476190000003</v>
       </c>
-      <c r="D95" s="4">
+      <c r="D95" s="3">
         <v>49056</v>
       </c>
       <c r="E95" s="3">
@@ -2609,7 +2666,7 @@
       <c r="F95">
         <v>76.900000000000006</v>
       </c>
-      <c r="G95" s="5">
+      <c r="G95" s="4">
         <v>4.2</v>
       </c>
     </row>
@@ -2623,7 +2680,7 @@
       <c r="C96">
         <v>4.7407818180000003</v>
       </c>
-      <c r="D96" s="4">
+      <c r="D96" s="3">
         <v>48499</v>
       </c>
       <c r="E96" s="3">
@@ -2632,7 +2689,7 @@
       <c r="F96">
         <v>76.900000000000006</v>
       </c>
-      <c r="G96" s="5">
+      <c r="G96" s="4">
         <v>4.2</v>
       </c>
     </row>
@@ -2646,7 +2703,7 @@
       <c r="C97">
         <v>4.7618095240000002</v>
       </c>
-      <c r="D97" s="4">
+      <c r="D97" s="3">
         <v>49730</v>
       </c>
       <c r="E97" s="3">
@@ -2655,7 +2712,7 @@
       <c r="F97">
         <v>77</v>
       </c>
-      <c r="G97" s="5">
+      <c r="G97" s="4">
         <v>4.3</v>
       </c>
     </row>
@@ -2669,7 +2726,7 @@
       <c r="C98">
         <v>4.759925</v>
       </c>
-      <c r="D98" s="4">
+      <c r="D98" s="3">
         <v>49215</v>
       </c>
       <c r="E98" s="3">
@@ -2678,7 +2735,7 @@
       <c r="F98">
         <v>77.8</v>
       </c>
-      <c r="G98" s="5">
+      <c r="G98" s="4">
         <v>4.2</v>
       </c>
     </row>
@@ -2692,7 +2749,7 @@
       <c r="C99">
         <v>4.8160249999999998</v>
       </c>
-      <c r="D99" s="4">
+      <c r="D99" s="3">
         <v>48042</v>
       </c>
       <c r="E99" s="3">
@@ -2701,7 +2758,7 @@
       <c r="F99">
         <v>77.7</v>
       </c>
-      <c r="G99" s="5">
+      <c r="G99" s="4">
         <v>4.5999999999999996</v>
       </c>
     </row>
@@ -2715,7 +2772,7 @@
       <c r="C100">
         <v>4.7618333330000002</v>
       </c>
-      <c r="D100" s="4">
+      <c r="D100" s="3">
         <v>49787</v>
       </c>
       <c r="E100" s="3">
@@ -2724,7 +2781,7 @@
       <c r="F100">
         <v>77.3</v>
       </c>
-      <c r="G100" s="5">
+      <c r="G100" s="4">
         <v>4.5</v>
       </c>
     </row>
@@ -2738,7 +2795,7 @@
       <c r="C101">
         <v>4.8124952380000003</v>
       </c>
-      <c r="D101" s="4">
+      <c r="D101" s="3">
         <v>51424</v>
       </c>
       <c r="E101" s="3">
@@ -2747,7 +2804,7 @@
       <c r="F101">
         <v>78.400000000000006</v>
       </c>
-      <c r="G101" s="5">
+      <c r="G101" s="4">
         <v>4.5999999999999996</v>
       </c>
     </row>
@@ -2761,7 +2818,7 @@
       <c r="C102">
         <v>4.7078499999999996</v>
       </c>
-      <c r="D102" s="4">
+      <c r="D102" s="3">
         <v>50561</v>
       </c>
       <c r="E102" s="3">
@@ -2770,7 +2827,7 @@
       <c r="F102">
         <v>78</v>
       </c>
-      <c r="G102" s="5">
+      <c r="G102" s="4">
         <v>4.3</v>
       </c>
     </row>
@@ -2784,7 +2841,7 @@
       <c r="C103">
         <v>4.7934954550000004</v>
       </c>
-      <c r="D103" s="4">
+      <c r="D103" s="3">
         <v>50642</v>
       </c>
       <c r="E103" s="3">
@@ -2793,7 +2850,7 @@
       <c r="F103">
         <v>78.5</v>
       </c>
-      <c r="G103" s="5">
+      <c r="G103" s="4">
         <v>4.5</v>
       </c>
     </row>
@@ -2807,7 +2864,7 @@
       <c r="C104">
         <v>4.7546333330000001</v>
       </c>
-      <c r="D104" s="4">
+      <c r="D104" s="3">
         <v>50873</v>
       </c>
       <c r="E104" s="3">
@@ -2816,7 +2873,7 @@
       <c r="F104">
         <v>79</v>
       </c>
-      <c r="G104" s="5">
+      <c r="G104" s="4">
         <v>4.5999999999999996</v>
       </c>
     </row>
@@ -2830,7 +2887,7 @@
       <c r="C105">
         <v>4.5774772730000004</v>
       </c>
-      <c r="D105" s="4">
+      <c r="D105" s="3">
         <v>51889</v>
       </c>
       <c r="E105" s="3">
@@ -2839,7 +2896,7 @@
       <c r="F105">
         <v>79</v>
       </c>
-      <c r="G105" s="5">
+      <c r="G105" s="4">
         <v>4.8</v>
       </c>
     </row>
@@ -2853,7 +2910,7 @@
       <c r="C106">
         <v>4.5499454549999996</v>
       </c>
-      <c r="D106" s="4">
+      <c r="D106" s="3">
         <v>51318</v>
       </c>
       <c r="E106" s="3">
@@ -2862,7 +2919,7 @@
       <c r="F106">
         <v>79.400000000000006</v>
       </c>
-      <c r="G106" s="5">
+      <c r="G106" s="4">
         <v>5</v>
       </c>
     </row>
@@ -2876,7 +2933,7 @@
       <c r="C107">
         <v>4.4246476189999999</v>
       </c>
-      <c r="D107" s="4">
+      <c r="D107" s="3">
         <v>51702</v>
       </c>
       <c r="E107" s="3">
@@ -2885,7 +2942,7 @@
       <c r="F107">
         <v>79.3</v>
       </c>
-      <c r="G107" s="5">
+      <c r="G107" s="4">
         <v>4.8</v>
       </c>
     </row>
@@ -2899,7 +2956,7 @@
       <c r="C108">
         <v>4.5458272729999996</v>
       </c>
-      <c r="D108" s="4">
+      <c r="D108" s="3">
         <v>52467</v>
       </c>
       <c r="E108" s="3">
@@ -2908,7 +2965,7 @@
       <c r="F108">
         <v>80.099999999999994</v>
       </c>
-      <c r="G108" s="5">
+      <c r="G108" s="4">
         <v>4.7</v>
       </c>
     </row>
@@ -2922,7 +2979,7 @@
       <c r="C109">
         <v>4.6380949999999999</v>
       </c>
-      <c r="D109" s="4">
+      <c r="D109" s="3">
         <v>53899</v>
       </c>
       <c r="E109" s="3">
@@ -2931,7 +2988,7 @@
       <c r="F109">
         <v>80.7</v>
       </c>
-      <c r="G109" s="5">
+      <c r="G109" s="4">
         <v>4.5999999999999996</v>
       </c>
     </row>
@@ -2945,7 +3002,7 @@
       <c r="C110">
         <v>4.482885714</v>
       </c>
-      <c r="D110" s="4">
+      <c r="D110" s="3">
         <v>56476</v>
       </c>
       <c r="E110" s="3">
@@ -2954,7 +3011,7 @@
       <c r="F110">
         <v>80.400000000000006</v>
       </c>
-      <c r="G110" s="5">
+      <c r="G110" s="4">
         <v>4.2</v>
       </c>
     </row>
@@ -2968,7 +3025,7 @@
       <c r="C111">
         <v>4.4254600000000002</v>
       </c>
-      <c r="D111" s="4">
+      <c r="D111" s="3">
         <v>58571</v>
       </c>
       <c r="E111" s="3">
@@ -2977,7 +3034,7 @@
       <c r="F111">
         <v>80.3</v>
       </c>
-      <c r="G111" s="5">
+      <c r="G111" s="4">
         <v>4.4000000000000004</v>
       </c>
     </row>
@@ -2991,7 +3048,7 @@
       <c r="C112">
         <v>4.5402304349999998</v>
       </c>
-      <c r="D112" s="4">
+      <c r="D112" s="3">
         <v>60269</v>
       </c>
       <c r="E112" s="3">
@@ -3000,7 +3057,7 @@
       <c r="F112">
         <v>80.599999999999994</v>
       </c>
-      <c r="G112" s="5">
+      <c r="G112" s="4">
         <v>4.9000000000000004</v>
       </c>
     </row>
@@ -3014,7 +3071,7 @@
       <c r="C113">
         <v>4.492811111</v>
       </c>
-      <c r="D113" s="4">
+      <c r="D113" s="3">
         <v>60119</v>
       </c>
       <c r="E113" s="3">
@@ -3023,7 +3080,7 @@
       <c r="F113">
         <v>80.2</v>
       </c>
-      <c r="G113" s="5">
+      <c r="G113" s="4">
         <v>5.3</v>
       </c>
     </row>
@@ -3037,7 +3094,7 @@
       <c r="C114">
         <v>4.5092761899999996</v>
       </c>
-      <c r="D114" s="4">
+      <c r="D114" s="3">
         <v>61150</v>
       </c>
       <c r="E114" s="3">
@@ -3046,7 +3103,7 @@
       <c r="F114">
         <v>80.599999999999994</v>
       </c>
-      <c r="G114" s="5">
+      <c r="G114" s="4">
         <v>5</v>
       </c>
     </row>
@@ -3060,7 +3117,7 @@
       <c r="C115">
         <v>4.5711954549999998</v>
       </c>
-      <c r="D115" s="4">
+      <c r="D115" s="3">
         <v>57289</v>
       </c>
       <c r="E115" s="3">
@@ -3069,7 +3126,7 @@
       <c r="F115">
         <v>80.8</v>
       </c>
-      <c r="G115" s="5">
+      <c r="G115" s="4">
         <v>4.9000000000000004</v>
       </c>
     </row>
@@ -3083,7 +3140,7 @@
       <c r="C116">
         <v>4.5458523810000004</v>
       </c>
-      <c r="D116" s="4">
+      <c r="D116" s="3">
         <v>52955</v>
       </c>
       <c r="E116" s="3">
@@ -3092,7 +3149,7 @@
       <c r="F116">
         <v>80.3</v>
       </c>
-      <c r="G116" s="5">
+      <c r="G116" s="4">
         <v>5</v>
       </c>
     </row>
@@ -3106,7 +3163,7 @@
       <c r="C117">
         <v>4.8025863639999997</v>
       </c>
-      <c r="D117" s="4">
+      <c r="D117" s="3">
         <v>53920</v>
       </c>
       <c r="E117" s="3">
@@ -3115,7 +3172,7 @@
       <c r="F117">
         <v>80.599999999999994</v>
       </c>
-      <c r="G117" s="5">
+      <c r="G117" s="4">
         <v>4.7</v>
       </c>
     </row>
@@ -3129,7 +3186,7 @@
       <c r="C118">
         <v>4.7892047619999998</v>
       </c>
-      <c r="D118" s="4">
+      <c r="D118" s="3">
         <v>52303</v>
       </c>
       <c r="E118" s="3">
@@ -3138,7 +3195,7 @@
       <c r="F118">
         <v>80.900000000000006</v>
       </c>
-      <c r="G118" s="5">
+      <c r="G118" s="4">
         <v>4.0999999999999996</v>
       </c>
     </row>
@@ -3152,7 +3209,7 @@
       <c r="C119">
         <v>4.8255136360000002</v>
       </c>
-      <c r="D119" s="4">
+      <c r="D119" s="3">
         <v>52327</v>
       </c>
       <c r="E119" s="3">
@@ -3161,7 +3218,7 @@
       <c r="F119">
         <v>80.400000000000006</v>
       </c>
-      <c r="G119" s="5">
+      <c r="G119" s="4">
         <v>4</v>
       </c>
     </row>
@@ -3175,7 +3232,7 @@
       <c r="C120">
         <v>4.9967636359999998</v>
       </c>
-      <c r="D120" s="4">
+      <c r="D120" s="3">
         <v>53547</v>
       </c>
       <c r="E120" s="3">
@@ -3184,7 +3241,7 @@
       <c r="F120">
         <v>80.8</v>
       </c>
-      <c r="G120" s="5">
+      <c r="G120" s="4">
         <v>4.2</v>
       </c>
     </row>
@@ -3198,7 +3255,7 @@
       <c r="C121">
         <v>5.0843526319999999</v>
       </c>
-      <c r="D121" s="4">
+      <c r="D121" s="3">
         <v>53916</v>
       </c>
       <c r="E121" s="3">
@@ -3207,7 +3264,7 @@
       <c r="F121">
         <v>81.5</v>
       </c>
-      <c r="G121" s="5">
+      <c r="G121" s="4">
         <v>4.9000000000000004</v>
       </c>
     </row>
@@ -3221,7 +3278,7 @@
       <c r="C122">
         <v>5.2230727269999999</v>
       </c>
-      <c r="D122" s="4">
+      <c r="D122" s="3">
         <v>53374</v>
       </c>
       <c r="E122" s="3">
@@ -3230,7 +3287,7 @@
       <c r="F122">
         <v>81.5</v>
       </c>
-      <c r="G122" s="5">
+      <c r="G122" s="4">
         <v>5.4</v>
       </c>
     </row>
@@ -3244,7 +3301,7 @@
       <c r="C123">
         <v>5.3182749999999999</v>
       </c>
-      <c r="D123" s="4">
+      <c r="D123" s="3">
         <v>54483</v>
       </c>
       <c r="E123" s="3">
@@ -3253,7 +3310,7 @@
       <c r="F123">
         <v>81.900000000000006</v>
       </c>
-      <c r="G123" s="5">
+      <c r="G123" s="4">
         <v>6.2</v>
       </c>
     </row>
@@ -3267,7 +3324,7 @@
       <c r="C124">
         <v>5.3032136359999997</v>
       </c>
-      <c r="D124" s="4">
+      <c r="D124" s="3">
         <v>56319</v>
       </c>
       <c r="E124" s="3">
@@ -3276,7 +3333,7 @@
       <c r="F124">
         <v>82.1</v>
       </c>
-      <c r="G124" s="5">
+      <c r="G124" s="4">
         <v>5.8</v>
       </c>
     </row>
@@ -3290,7 +3347,7 @@
       <c r="C125">
         <v>5.2915315789999999</v>
       </c>
-      <c r="D125" s="4">
+      <c r="D125" s="3">
         <v>54008</v>
       </c>
       <c r="E125" s="3">
@@ -3299,7 +3356,7 @@
       <c r="F125">
         <v>82.3</v>
       </c>
-      <c r="G125" s="5">
+      <c r="G125" s="4">
         <v>5.2</v>
       </c>
     </row>
@@ -3313,7 +3370,7 @@
       <c r="C126">
         <v>5.477766667</v>
       </c>
-      <c r="D126" s="4">
+      <c r="D126" s="3">
         <v>54121</v>
       </c>
       <c r="E126" s="3">
@@ -3322,7 +3379,7 @@
       <c r="F126">
         <v>82.7</v>
       </c>
-      <c r="G126" s="5">
+      <c r="G126" s="4">
         <v>4.5</v>
       </c>
     </row>
@@ -3336,7 +3393,7 @@
       <c r="C127">
         <v>5.6093190479999997</v>
       </c>
-      <c r="D127" s="4">
+      <c r="D127" s="3">
         <v>55828</v>
       </c>
       <c r="E127" s="3">
@@ -3345,7 +3402,7 @@
       <c r="F127">
         <v>82.9</v>
       </c>
-      <c r="G127" s="5">
+      <c r="G127" s="4">
         <v>4.5</v>
       </c>
     </row>
@@ -3359,7 +3416,7 @@
       <c r="C128">
         <v>5.8433863639999997</v>
       </c>
-      <c r="D128" s="4">
+      <c r="D128" s="3">
         <v>56735</v>
       </c>
       <c r="E128" s="3">
@@ -3368,7 +3425,7 @@
       <c r="F128">
         <v>82.9</v>
       </c>
-      <c r="G128" s="5">
+      <c r="G128" s="4">
         <v>4.5999999999999996</v>
       </c>
     </row>
@@ -3382,7 +3439,7 @@
       <c r="C129">
         <v>5.9127363639999997</v>
       </c>
-      <c r="D129" s="4">
+      <c r="D129" s="3">
         <v>56958</v>
       </c>
       <c r="E129" s="3">
@@ -3391,7 +3448,7 @@
       <c r="F129">
         <v>83.5</v>
       </c>
-      <c r="G129" s="5">
+      <c r="G129" s="4">
         <v>4.8</v>
       </c>
     </row>
@@ -3405,7 +3462,7 @@
       <c r="C130">
         <v>5.8246399999999996</v>
       </c>
-      <c r="D130" s="4">
+      <c r="D130" s="3">
         <v>56294</v>
       </c>
       <c r="E130" s="3">
@@ -3414,7 +3471,7 @@
       <c r="F130">
         <v>83.7</v>
       </c>
-      <c r="G130" s="5">
+      <c r="G130" s="4">
         <v>5.2</v>
       </c>
     </row>
@@ -3428,7 +3485,7 @@
       <c r="C131">
         <v>5.7750521739999998</v>
       </c>
-      <c r="D131" s="4">
+      <c r="D131" s="3">
         <v>56347</v>
       </c>
       <c r="E131" s="3">
@@ -3437,7 +3494,7 @@
       <c r="F131">
         <v>83.6</v>
       </c>
-      <c r="G131" s="5">
+      <c r="G131" s="4">
         <v>5</v>
       </c>
     </row>
@@ -3451,7 +3508,7 @@
       <c r="C132">
         <v>5.7892136360000004</v>
       </c>
-      <c r="D132" s="4">
+      <c r="D132" s="3">
         <v>56903</v>
       </c>
       <c r="E132" s="3">
@@ -3460,7 +3517,7 @@
       <c r="F132">
         <v>84.1</v>
       </c>
-      <c r="G132" s="5">
+      <c r="G132" s="4">
         <v>4.9000000000000004</v>
       </c>
     </row>
@@ -3474,7 +3531,7 @@
       <c r="C133">
         <v>5.5964052630000003</v>
       </c>
-      <c r="D133" s="4">
+      <c r="D133" s="3">
         <v>55520</v>
       </c>
       <c r="E133" s="3">
@@ -3483,7 +3540,7 @@
       <c r="F133">
         <v>84.4</v>
       </c>
-      <c r="G133" s="5">
+      <c r="G133" s="4">
         <v>4.0999999999999996</v>
       </c>
     </row>
@@ -3497,7 +3554,7 @@
       <c r="C134">
         <v>5.5049181819999999</v>
       </c>
-      <c r="D134" s="4">
+      <c r="D134" s="3">
         <v>56444</v>
       </c>
       <c r="E134" s="3">
@@ -3506,7 +3563,7 @@
       <c r="F134">
         <v>84.4</v>
       </c>
-      <c r="G134" s="5">
+      <c r="G134" s="4">
         <v>3.8</v>
       </c>
     </row>
@@ -3520,7 +3577,7 @@
       <c r="C135">
         <v>5.3322380950000001</v>
       </c>
-      <c r="D135" s="4">
+      <c r="D135" s="3">
         <v>56869</v>
       </c>
       <c r="E135" s="3">
@@ -3529,7 +3586,7 @@
       <c r="F135">
         <v>85</v>
       </c>
-      <c r="G135" s="5">
+      <c r="G135" s="4">
         <v>3.5</v>
       </c>
     </row>
@@ -3543,7 +3600,7 @@
       <c r="C136">
         <v>5.3078263159999999</v>
       </c>
-      <c r="D136" s="4">
+      <c r="D136" s="3">
         <v>55881</v>
       </c>
       <c r="E136" s="3">
@@ -3552,7 +3609,7 @@
       <c r="F136">
         <v>84</v>
       </c>
-      <c r="G136" s="5">
+      <c r="G136" s="4">
         <v>4.0999999999999996</v>
       </c>
     </row>
@@ -3566,7 +3623,7 @@
       <c r="C137">
         <v>5.0800136360000003</v>
       </c>
-      <c r="D137" s="4">
+      <c r="D137" s="3">
         <v>56515</v>
       </c>
       <c r="E137" s="3">
@@ -3575,7 +3632,7 @@
       <c r="F137">
         <v>84.7</v>
       </c>
-      <c r="G137" s="5">
+      <c r="G137" s="4">
         <v>4.5</v>
       </c>
     </row>
@@ -3589,7 +3646,7 @@
       <c r="C138">
         <v>5.0313499999999998</v>
       </c>
-      <c r="D138" s="4">
+      <c r="D138" s="3">
         <v>55352</v>
       </c>
       <c r="E138" s="3">
@@ -3598,7 +3655,7 @@
       <c r="F138">
         <v>83.9</v>
       </c>
-      <c r="G138" s="5">
+      <c r="G138" s="4">
         <v>4.7</v>
       </c>
     </row>
@@ -3612,7 +3669,7 @@
       <c r="C139">
         <v>5.0326000000000004</v>
       </c>
-      <c r="D139" s="4">
+      <c r="D139" s="3">
         <v>56865</v>
       </c>
       <c r="E139" s="3">
@@ -3621,7 +3678,7 @@
       <c r="F139">
         <v>83.8</v>
       </c>
-      <c r="G139" s="5">
+      <c r="G139" s="4">
         <v>4.2</v>
       </c>
     </row>
@@ -3635,7 +3692,7 @@
       <c r="C140">
         <v>5.0098608699999998</v>
       </c>
-      <c r="D140" s="4">
+      <c r="D140" s="3">
         <v>55722</v>
       </c>
       <c r="E140" s="3">
@@ -3644,7 +3701,7 @@
       <c r="F140">
         <v>83.3</v>
       </c>
-      <c r="G140" s="5">
+      <c r="G140" s="4">
         <v>3.7</v>
       </c>
     </row>
@@ -3658,7 +3715,7 @@
       <c r="C141">
         <v>4.9970400000000001</v>
       </c>
-      <c r="D141" s="4">
+      <c r="D141" s="3">
         <v>54635</v>
       </c>
       <c r="E141" s="3">
@@ -3667,7 +3724,7 @@
       <c r="F141">
         <v>83.1</v>
       </c>
-      <c r="G141" s="5">
+      <c r="G141" s="4">
         <v>3.3</v>
       </c>
     </row>
@@ -3681,7 +3738,7 @@
       <c r="C142">
         <v>4.8925363639999997</v>
       </c>
-      <c r="D142" s="4">
+      <c r="D142" s="3">
         <v>54210</v>
       </c>
       <c r="E142" s="3">
@@ -3690,7 +3747,7 @@
       <c r="F142">
         <v>82.1</v>
       </c>
-      <c r="G142" s="5">
+      <c r="G142" s="4">
         <v>3.1</v>
       </c>
     </row>
@@ -3704,7 +3761,7 @@
       <c r="C143">
         <v>4.4115434779999996</v>
       </c>
-      <c r="D143" s="4">
+      <c r="D143" s="3">
         <v>53042</v>
       </c>
       <c r="E143" s="3">
@@ -3713,7 +3770,7 @@
       <c r="F143">
         <v>81.900000000000006</v>
       </c>
-      <c r="G143" s="5">
+      <c r="G143" s="4">
         <v>3.1</v>
       </c>
     </row>
@@ -3727,7 +3784,7 @@
       <c r="C144">
         <v>2.7845949999999999</v>
       </c>
-      <c r="D144" s="4">
+      <c r="D144" s="3">
         <v>52166</v>
       </c>
       <c r="E144" s="3">
@@ -3736,7 +3793,7 @@
       <c r="F144">
         <v>80.8</v>
       </c>
-      <c r="G144" s="5">
+      <c r="G144" s="4">
         <v>2.8</v>
       </c>
     </row>
@@ -3750,7 +3807,7 @@
       <c r="C145">
         <v>1.652504762</v>
       </c>
-      <c r="D145" s="4">
+      <c r="D145" s="3">
         <v>50281</v>
       </c>
       <c r="E145" s="3">
@@ -3759,7 +3816,7 @@
       <c r="F145">
         <v>80.400000000000006</v>
       </c>
-      <c r="G145" s="5">
+      <c r="G145" s="4">
         <v>2.8</v>
       </c>
     </row>
@@ -3773,7 +3830,7 @@
       <c r="C146">
         <v>1.325971429</v>
       </c>
-      <c r="D146" s="4">
+      <c r="D146" s="3">
         <v>50090</v>
       </c>
       <c r="E146" s="3">
@@ -3782,7 +3839,7 @@
       <c r="F146">
         <v>79.7</v>
       </c>
-      <c r="G146" s="5">
+      <c r="G146" s="4">
         <v>1</v>
       </c>
     </row>
@@ -3796,7 +3853,7 @@
       <c r="C147">
         <v>0.89733499999999999</v>
       </c>
-      <c r="D147" s="4">
+      <c r="D147" s="3">
         <v>49133</v>
       </c>
       <c r="E147" s="3">
@@ -3805,7 +3862,7 @@
       <c r="F147">
         <v>79.599999999999994</v>
       </c>
-      <c r="G147" s="5">
+      <c r="G147" s="4">
         <v>-1.8</v>
       </c>
     </row>
@@ -3819,7 +3876,7 @@
       <c r="C148">
         <v>0.52239545499999995</v>
       </c>
-      <c r="D148" s="4">
+      <c r="D148" s="3">
         <v>50242</v>
       </c>
       <c r="E148" s="3">
@@ -3828,7 +3885,7 @@
       <c r="F148">
         <v>79</v>
       </c>
-      <c r="G148" s="5">
+      <c r="G148" s="4">
         <v>-2.9</v>
       </c>
     </row>
@@ -3842,7 +3899,7 @@
       <c r="C149">
         <v>0.40991499999999997</v>
       </c>
-      <c r="D149" s="4">
+      <c r="D149" s="3">
         <v>50866</v>
       </c>
       <c r="E149" s="3">
@@ -3851,7 +3908,7 @@
       <c r="F149">
         <v>79.5</v>
       </c>
-      <c r="G149" s="5">
+      <c r="G149" s="4">
         <v>-1.8</v>
       </c>
     </row>
@@ -3865,7 +3922,7 @@
       <c r="C150">
         <v>0.41327368399999997</v>
       </c>
-      <c r="D150" s="4">
+      <c r="D150" s="3">
         <v>48793</v>
       </c>
       <c r="E150" s="3">
@@ -3874,7 +3931,7 @@
       <c r="F150">
         <v>78.8</v>
       </c>
-      <c r="G150" s="5">
+      <c r="G150" s="4">
         <v>0.5</v>
       </c>
     </row>
@@ -3888,7 +3945,7 @@
       <c r="C151">
         <v>0.41580454500000003</v>
       </c>
-      <c r="D151" s="4">
+      <c r="D151" s="3">
         <v>50054</v>
       </c>
       <c r="E151" s="3">
@@ -3897,7 +3954,7 @@
       <c r="F151">
         <v>79.099999999999994</v>
       </c>
-      <c r="G151" s="5">
+      <c r="G151" s="4">
         <v>1.2</v>
       </c>
     </row>
@@ -3911,7 +3968,7 @@
       <c r="C152">
         <v>0.41730869599999998</v>
       </c>
-      <c r="D152" s="4">
+      <c r="D152" s="3">
         <v>51332</v>
       </c>
       <c r="E152" s="3">
@@ -3920,7 +3977,7 @@
       <c r="F152">
         <v>79.5</v>
       </c>
-      <c r="G152" s="5">
+      <c r="G152" s="4">
         <v>0.9</v>
       </c>
     </row>
@@ -3934,7 +3991,7 @@
       <c r="C153">
         <v>0.42198999999999998</v>
       </c>
-      <c r="D153" s="4">
+      <c r="D153" s="3">
         <v>50351</v>
       </c>
       <c r="E153" s="3">
@@ -3943,7 +4000,7 @@
       <c r="F153">
         <v>79</v>
       </c>
-      <c r="G153" s="5">
+      <c r="G153" s="4">
         <v>0.8</v>
       </c>
     </row>
@@ -3957,7 +4014,7 @@
       <c r="C154">
         <v>0.430240909</v>
       </c>
-      <c r="D154" s="4">
+      <c r="D154" s="3">
         <v>51973</v>
       </c>
       <c r="E154" s="3">
@@ -3966,7 +4023,7 @@
       <c r="F154">
         <v>79.2</v>
       </c>
-      <c r="G154" s="5">
+      <c r="G154" s="4">
         <v>0.7</v>
       </c>
     </row>
@@ -3980,7 +4037,7 @@
       <c r="C155">
         <v>0.44721363600000003</v>
       </c>
-      <c r="D155" s="4">
+      <c r="D155" s="3">
         <v>52677</v>
       </c>
       <c r="E155" s="3">
@@ -3989,7 +4046,7 @@
       <c r="F155">
         <v>79.400000000000006</v>
       </c>
-      <c r="G155" s="5">
+      <c r="G155" s="4">
         <v>0.6</v>
       </c>
     </row>
@@ -4003,7 +4060,7 @@
       <c r="C156">
         <v>0.45090952400000001</v>
       </c>
-      <c r="D156" s="4">
+      <c r="D156" s="3">
         <v>51785</v>
       </c>
       <c r="E156" s="3">
@@ -4012,7 +4069,7 @@
       <c r="F156">
         <v>79.5</v>
       </c>
-      <c r="G156" s="5">
+      <c r="G156" s="4">
         <v>0.7</v>
       </c>
     </row>
@@ -4026,7 +4083,7 @@
       <c r="C157">
         <v>0.44915714299999998</v>
       </c>
-      <c r="D157" s="4">
+      <c r="D157" s="3">
         <v>52999</v>
       </c>
       <c r="E157" s="3">
@@ -4035,7 +4092,7 @@
       <c r="F157">
         <v>79.8</v>
       </c>
-      <c r="G157" s="5">
+      <c r="G157" s="4">
         <v>0.7</v>
       </c>
     </row>
@@ -4049,7 +4106,7 @@
       <c r="C158">
         <v>0.45450000000000002</v>
       </c>
-      <c r="D158" s="4">
+      <c r="D158" s="3">
         <v>52587</v>
       </c>
       <c r="E158" s="3">
@@ -4058,7 +4115,7 @@
       <c r="F158">
         <v>79.2</v>
       </c>
-      <c r="G158" s="5">
+      <c r="G158" s="4">
         <v>2</v>
       </c>
     </row>
@@ -4072,7 +4129,7 @@
       <c r="C159">
         <v>0.46724500000000002</v>
       </c>
-      <c r="D159" s="4">
+      <c r="D159" s="3">
         <v>52082</v>
       </c>
       <c r="E159" s="3">
@@ -4081,7 +4138,7 @@
       <c r="F159">
         <v>80.5</v>
       </c>
-      <c r="G159" s="5">
+      <c r="G159" s="4">
         <v>4.5999999999999996</v>
       </c>
     </row>
@@ -4095,7 +4152,7 @@
       <c r="C160">
         <v>0.47125217400000002</v>
       </c>
-      <c r="D160" s="4">
+      <c r="D160" s="3">
         <v>54474</v>
       </c>
       <c r="E160" s="3">
@@ -4104,7 +4161,7 @@
       <c r="F160">
         <v>81.2</v>
       </c>
-      <c r="G160" s="5">
+      <c r="G160" s="4">
         <v>5</v>
       </c>
     </row>
@@ -4118,7 +4175,7 @@
       <c r="C161">
         <v>0.47263500000000003</v>
       </c>
-      <c r="D161" s="4">
+      <c r="D161" s="3">
         <v>53815</v>
       </c>
       <c r="E161" s="3">
@@ -4127,7 +4184,7 @@
       <c r="F161">
         <v>80.900000000000006</v>
       </c>
-      <c r="G161" s="5">
+      <c r="G161" s="4">
         <v>3.8</v>
       </c>
     </row>
@@ -4141,7 +4198,7 @@
       <c r="C162">
         <v>0.48417894700000003</v>
       </c>
-      <c r="D162" s="4">
+      <c r="D162" s="3">
         <v>54011</v>
       </c>
       <c r="E162" s="3">
@@ -4150,7 +4207,7 @@
       <c r="F162">
         <v>81.400000000000006</v>
       </c>
-      <c r="G162" s="5">
+      <c r="G162" s="4">
         <v>1.3</v>
       </c>
     </row>
@@ -4164,7 +4221,7 @@
       <c r="C163">
         <v>0.48700454500000001</v>
       </c>
-      <c r="D163" s="4">
+      <c r="D163" s="3">
         <v>56144</v>
       </c>
       <c r="E163" s="3">
@@ -4173,7 +4230,7 @@
       <c r="F163">
         <v>81.5</v>
       </c>
-      <c r="G163" s="5">
+      <c r="G163" s="4">
         <v>1</v>
       </c>
     </row>
@@ -4187,7 +4244,7 @@
       <c r="C164">
         <v>0.48998181800000001</v>
       </c>
-      <c r="D164" s="4">
+      <c r="D164" s="3">
         <v>56373</v>
       </c>
       <c r="E164" s="3">
@@ -4196,7 +4253,7 @@
       <c r="F164">
         <v>81.599999999999994</v>
       </c>
-      <c r="G164" s="5">
+      <c r="G164" s="4">
         <v>1.2</v>
       </c>
     </row>
@@ -4210,7 +4267,7 @@
       <c r="C165">
         <v>0.49097142900000001</v>
       </c>
-      <c r="D165" s="4">
+      <c r="D165" s="3">
         <v>55913</v>
       </c>
       <c r="E165" s="3">
@@ -4219,7 +4276,7 @@
       <c r="F165">
         <v>81.7</v>
       </c>
-      <c r="G165" s="5">
+      <c r="G165" s="4">
         <v>1.3</v>
       </c>
     </row>
@@ -4233,7 +4290,7 @@
       <c r="C166">
         <v>0.50096818200000004</v>
       </c>
-      <c r="D166" s="4">
+      <c r="D166" s="3">
         <v>56808</v>
       </c>
       <c r="E166" s="3">
@@ -4242,7 +4299,7 @@
       <c r="F166">
         <v>81.900000000000006</v>
       </c>
-      <c r="G166" s="5">
+      <c r="G166" s="4">
         <v>1.5</v>
       </c>
     </row>
@@ -4256,7 +4313,7 @@
       <c r="C167">
         <v>0.508271429</v>
       </c>
-      <c r="D167" s="4">
+      <c r="D167" s="3">
         <v>55846</v>
       </c>
       <c r="E167" s="3">
@@ -4265,7 +4322,7 @@
       <c r="F167">
         <v>82.2</v>
       </c>
-      <c r="G167" s="5">
+      <c r="G167" s="4">
         <v>1.7</v>
       </c>
     </row>
@@ -4279,7 +4336,7 @@
       <c r="C168">
         <v>0.50856818199999998</v>
       </c>
-      <c r="D168" s="4">
+      <c r="D168" s="3">
         <v>57095</v>
       </c>
       <c r="E168" s="3">
@@ -4288,7 +4345,7 @@
       <c r="F168">
         <v>81.900000000000006</v>
       </c>
-      <c r="G168" s="5">
+      <c r="G168" s="4">
         <v>1.8</v>
       </c>
     </row>
@@ -4302,7 +4359,7 @@
       <c r="C169">
         <v>0.51731904799999995</v>
       </c>
-      <c r="D169" s="4">
+      <c r="D169" s="3">
         <v>57938</v>
       </c>
       <c r="E169" s="3">
@@ -4311,7 +4368,7 @@
       <c r="F169">
         <v>81.2</v>
       </c>
-      <c r="G169" s="5">
+      <c r="G169" s="4">
         <v>1.9</v>
       </c>
     </row>
@@ -4325,7 +4382,7 @@
       <c r="C170">
         <v>0.50590999999999997</v>
       </c>
-      <c r="D170" s="4">
+      <c r="D170" s="3">
         <v>56729</v>
       </c>
       <c r="E170" s="3">
@@ -4334,7 +4391,7 @@
       <c r="F170">
         <v>81.5</v>
       </c>
-      <c r="G170" s="5">
+      <c r="G170" s="4">
         <v>2.7</v>
       </c>
     </row>
@@ -4348,7 +4405,7 @@
       <c r="C171">
         <v>0.50836999999999999</v>
       </c>
-      <c r="D171" s="4">
+      <c r="D171" s="3">
         <v>54607</v>
       </c>
       <c r="E171" s="3">
@@ -4357,7 +4414,7 @@
       <c r="F171">
         <v>81.900000000000006</v>
       </c>
-      <c r="G171" s="5">
+      <c r="G171" s="4">
         <v>2.6</v>
       </c>
     </row>
@@ -4371,7 +4428,7 @@
       <c r="C172">
         <v>0.51543043499999996</v>
       </c>
-      <c r="D172" s="4">
+      <c r="D172" s="3">
         <v>56047</v>
       </c>
       <c r="E172" s="3">
@@ -4380,7 +4437,7 @@
       <c r="F172">
         <v>82</v>
       </c>
-      <c r="G172" s="5">
+      <c r="G172" s="4">
         <v>2.8</v>
       </c>
     </row>
@@ -4394,7 +4451,7 @@
       <c r="C173">
         <v>0.52400555599999998</v>
       </c>
-      <c r="D173" s="4">
+      <c r="D173" s="3">
         <v>54914</v>
       </c>
       <c r="E173" s="3">
@@ -4403,7 +4460,7 @@
       <c r="F173">
         <v>81.3</v>
       </c>
-      <c r="G173" s="5">
+      <c r="G173" s="4">
         <v>2.1</v>
       </c>
     </row>
@@ -4417,7 +4474,7 @@
       <c r="C174">
         <v>0.52166500000000005</v>
       </c>
-      <c r="D174" s="4">
+      <c r="D174" s="3">
         <v>60662</v>
       </c>
       <c r="E174" s="3">
@@ -4426,7 +4483,7 @@
       <c r="F174">
         <v>82.1</v>
       </c>
-      <c r="G174" s="5">
+      <c r="G174" s="4">
         <v>2.4</v>
       </c>
     </row>
@@ -4440,7 +4497,7 @@
       <c r="C175">
         <v>0.53108181799999998</v>
       </c>
-      <c r="D175" s="4">
+      <c r="D175" s="3">
         <v>56134</v>
       </c>
       <c r="E175" s="3">
@@ -4449,7 +4506,7 @@
       <c r="F175">
         <v>82.1</v>
       </c>
-      <c r="G175" s="5">
+      <c r="G175" s="4">
         <v>2.5</v>
       </c>
     </row>
@@ -4463,7 +4520,7 @@
       <c r="C176">
         <v>0.52280000000000004</v>
       </c>
-      <c r="D176" s="4">
+      <c r="D176" s="3">
         <v>57069</v>
       </c>
       <c r="E176" s="3">
@@ -4472,7 +4529,7 @@
       <c r="F176">
         <v>82.2</v>
       </c>
-      <c r="G176" s="5">
+      <c r="G176" s="4">
         <v>2.8</v>
       </c>
     </row>
@@ -4486,7 +4543,7 @@
       <c r="C177">
         <v>0.53796363599999997</v>
       </c>
-      <c r="D177" s="4">
+      <c r="D177" s="3">
         <v>56049</v>
       </c>
       <c r="E177" s="3">
@@ -4495,7 +4552,7 @@
       <c r="F177">
         <v>81.900000000000006</v>
       </c>
-      <c r="G177" s="5">
+      <c r="G177" s="4">
         <v>2.7</v>
       </c>
     </row>
@@ -4509,7 +4566,7 @@
       <c r="C178">
         <v>0.548559091</v>
       </c>
-      <c r="D178" s="4">
+      <c r="D178" s="3">
         <v>57474</v>
       </c>
       <c r="E178" s="3">
@@ -4518,7 +4575,7 @@
       <c r="F178">
         <v>82</v>
       </c>
-      <c r="G178" s="5">
+      <c r="G178" s="4">
         <v>2.2000000000000002</v>
       </c>
     </row>
@@ -4532,7 +4589,7 @@
       <c r="C179">
         <v>0.53580476200000005</v>
       </c>
-      <c r="D179" s="4">
+      <c r="D179" s="3">
         <v>57839</v>
       </c>
       <c r="E179" s="3">
@@ -4541,7 +4598,7 @@
       <c r="F179">
         <v>81.3</v>
       </c>
-      <c r="G179" s="5">
+      <c r="G179" s="4">
         <v>1.9</v>
       </c>
     </row>
@@ -4555,7 +4612,7 @@
       <c r="C180">
         <v>0.53472272700000001</v>
       </c>
-      <c r="D180" s="4">
+      <c r="D180" s="3">
         <v>57363</v>
       </c>
       <c r="E180" s="3">
@@ -4564,7 +4621,7 @@
       <c r="F180">
         <v>82.3</v>
       </c>
-      <c r="G180" s="5">
+      <c r="G180" s="4">
         <v>1.9</v>
       </c>
     </row>
@@ -4578,7 +4635,7 @@
       <c r="C181">
         <v>0.52005000000000001</v>
       </c>
-      <c r="D181" s="4">
+      <c r="D181" s="3">
         <v>56375</v>
       </c>
       <c r="E181" s="3">
@@ -4587,7 +4644,7 @@
       <c r="F181">
         <v>83</v>
       </c>
-      <c r="G181" s="5">
+      <c r="G181" s="4">
         <v>1.9</v>
       </c>
     </row>
@@ -4601,7 +4658,7 @@
       <c r="C182">
         <v>0.51565714299999998</v>
       </c>
-      <c r="D182" s="4">
+      <c r="D182" s="3">
         <v>58406</v>
       </c>
       <c r="E182" s="3">
@@ -4610,7 +4667,7 @@
       <c r="F182">
         <v>83.3</v>
       </c>
-      <c r="G182" s="5">
+      <c r="G182" s="4">
         <v>1.2</v>
       </c>
     </row>
@@ -4624,7 +4681,7 @@
       <c r="C183">
         <v>0.49925714300000001</v>
       </c>
-      <c r="D183" s="4">
+      <c r="D183" s="3">
         <v>56645</v>
       </c>
       <c r="E183" s="3">
@@ -4633,7 +4690,7 @@
       <c r="F183">
         <v>82.8</v>
       </c>
-      <c r="G183" s="5">
+      <c r="G183" s="4">
         <v>0.8</v>
       </c>
     </row>
@@ -4647,7 +4704,7 @@
       <c r="C184">
         <v>0.48999545500000002</v>
       </c>
-      <c r="D184" s="4">
+      <c r="D184" s="3">
         <v>58461</v>
       </c>
       <c r="E184" s="3">
@@ -4656,7 +4713,7 @@
       <c r="F184">
         <v>82.9</v>
       </c>
-      <c r="G184" s="5">
+      <c r="G184" s="4">
         <v>0.6</v>
       </c>
     </row>
@@ -4670,7 +4727,7 @@
       <c r="C185">
         <v>0.48611052599999999</v>
       </c>
-      <c r="D185" s="4">
+      <c r="D185" s="3">
         <v>59113</v>
       </c>
       <c r="E185" s="3">
@@ -4679,7 +4736,7 @@
       <c r="F185">
         <v>82.5</v>
       </c>
-      <c r="G185" s="5">
+      <c r="G185" s="4">
         <v>1.3</v>
       </c>
     </row>
@@ -4693,7 +4750,7 @@
       <c r="C186">
         <v>0.48480000000000001</v>
       </c>
-      <c r="D186" s="4">
+      <c r="D186" s="3">
         <v>59100</v>
       </c>
       <c r="E186" s="3">
@@ -4702,7 +4759,7 @@
       <c r="F186">
         <v>83.7</v>
       </c>
-      <c r="G186" s="5">
+      <c r="G186" s="4">
         <v>1.5</v>
       </c>
     </row>
@@ -4716,7 +4773,7 @@
       <c r="C187">
         <v>0.48588421100000001</v>
       </c>
-      <c r="D187" s="4">
+      <c r="D187" s="3">
         <v>58127</v>
       </c>
       <c r="E187" s="3">
@@ -4725,7 +4782,7 @@
       <c r="F187">
         <v>82.7</v>
       </c>
-      <c r="G187" s="5">
+      <c r="G187" s="4">
         <v>1.6</v>
       </c>
     </row>
@@ -4739,7 +4796,7 @@
       <c r="C188">
         <v>0.46455454499999999</v>
       </c>
-      <c r="D188" s="4">
+      <c r="D188" s="3">
         <v>58212</v>
       </c>
       <c r="E188" s="3">
@@ -4748,7 +4805,7 @@
       <c r="F188">
         <v>83.8</v>
       </c>
-      <c r="G188" s="5">
+      <c r="G188" s="4">
         <v>1.5</v>
       </c>
     </row>
@@ -4762,7 +4819,7 @@
       <c r="C189">
         <v>0.45004545499999998</v>
       </c>
-      <c r="D189" s="4">
+      <c r="D189" s="3">
         <v>59414</v>
       </c>
       <c r="E189" s="3">
@@ -4771,7 +4828,7 @@
       <c r="F189">
         <v>84.3</v>
       </c>
-      <c r="G189" s="5">
+      <c r="G189" s="4">
         <v>1.7</v>
       </c>
     </row>
@@ -4785,7 +4842,7 @@
       <c r="C190">
         <v>0.42707000000000001</v>
       </c>
-      <c r="D190" s="4">
+      <c r="D190" s="3">
         <v>57477</v>
       </c>
       <c r="E190" s="3">
@@ -4794,7 +4851,7 @@
       <c r="F190">
         <v>83.4</v>
       </c>
-      <c r="G190" s="5">
+      <c r="G190" s="4">
         <v>1.8</v>
       </c>
     </row>
@@ -4808,7 +4865,7 @@
       <c r="C191">
         <v>0.43338695700000002</v>
       </c>
-      <c r="D191" s="4">
+      <c r="D191" s="3">
         <v>57204</v>
       </c>
       <c r="E191" s="3">
@@ -4817,7 +4874,7 @@
       <c r="F191">
         <v>83.7</v>
       </c>
-      <c r="G191" s="5">
+      <c r="G191" s="4">
         <v>1.7</v>
       </c>
     </row>
@@ -4831,7 +4888,7 @@
       <c r="C192">
         <v>0.42562272699999998</v>
       </c>
-      <c r="D192" s="4">
+      <c r="D192" s="3">
         <v>56492</v>
       </c>
       <c r="E192" s="3">
@@ -4840,7 +4897,7 @@
       <c r="F192">
         <v>83.9</v>
       </c>
-      <c r="G192" s="5">
+      <c r="G192" s="4">
         <v>1.5</v>
       </c>
     </row>
@@ -4854,7 +4911,7 @@
       <c r="C193">
         <v>0.43086315800000002</v>
       </c>
-      <c r="D193" s="4">
+      <c r="D193" s="3">
         <v>57998</v>
       </c>
       <c r="E193" s="3">
@@ -4863,7 +4920,7 @@
       <c r="F193">
         <v>83.6</v>
       </c>
-      <c r="G193" s="5">
+      <c r="G193" s="4">
         <v>1.2</v>
       </c>
     </row>
@@ -4877,7 +4934,7 @@
       <c r="C194">
         <v>0.40969090899999999</v>
       </c>
-      <c r="D194" s="4">
+      <c r="D194" s="3">
         <v>57292</v>
       </c>
       <c r="E194" s="3">
@@ -4886,7 +4943,7 @@
       <c r="F194">
         <v>83.5</v>
       </c>
-      <c r="G194" s="5">
+      <c r="G194" s="4">
         <v>1.1000000000000001</v>
       </c>
     </row>
@@ -4900,7 +4957,7 @@
       <c r="C195">
         <v>0.42613499999999999</v>
       </c>
-      <c r="D195" s="4">
+      <c r="D195" s="3">
         <v>56998</v>
       </c>
       <c r="E195" s="3">
@@ -4909,7 +4966,7 @@
       <c r="F195">
         <v>84.2</v>
       </c>
-      <c r="G195" s="5">
+      <c r="G195" s="4">
         <v>1</v>
       </c>
     </row>
@@ -4923,7 +4980,7 @@
       <c r="C196">
         <v>0.43531999999999998</v>
       </c>
-      <c r="D196" s="4">
+      <c r="D196" s="3">
         <v>59159</v>
       </c>
       <c r="E196" s="3">
@@ -4932,7 +4989,7 @@
       <c r="F196">
         <v>84.1</v>
       </c>
-      <c r="G196" s="5">
+      <c r="G196" s="4">
         <v>0.5</v>
       </c>
     </row>
@@ -4946,7 +5003,7 @@
       <c r="C197">
         <v>0.43964761899999999</v>
       </c>
-      <c r="D197" s="4">
+      <c r="D197" s="3">
         <v>58321</v>
       </c>
       <c r="E197" s="3">
@@ -4955,7 +5012,7 @@
       <c r="F197">
         <v>84.3</v>
       </c>
-      <c r="G197" s="5">
+      <c r="G197" s="4">
         <v>1.4</v>
       </c>
     </row>
@@ -4969,7 +5026,7 @@
       <c r="C198">
         <v>0.43359999999999999</v>
       </c>
-      <c r="D198" s="4">
+      <c r="D198" s="3">
         <v>61454</v>
       </c>
       <c r="E198" s="3">
@@ -4978,7 +5035,7 @@
       <c r="F198">
         <v>84.5</v>
       </c>
-      <c r="G198" s="5">
+      <c r="G198" s="4">
         <v>1.6</v>
       </c>
     </row>
@@ -4992,7 +5049,7 @@
       <c r="C199">
         <v>0.42515999999999998</v>
       </c>
-      <c r="D199" s="4">
+      <c r="D199" s="3">
         <v>61866</v>
       </c>
       <c r="E199" s="3">
@@ -5001,7 +5058,7 @@
       <c r="F199">
         <v>84.7</v>
       </c>
-      <c r="G199" s="5">
+      <c r="G199" s="4">
         <v>2.2000000000000002</v>
       </c>
     </row>
@@ -5015,7 +5072,7 @@
       <c r="C200">
         <v>0.43012608699999999</v>
       </c>
-      <c r="D200" s="4">
+      <c r="D200" s="3">
         <v>59298</v>
       </c>
       <c r="E200" s="3">
@@ -5024,7 +5081,7 @@
       <c r="F200">
         <v>84.9</v>
       </c>
-      <c r="G200" s="5">
+      <c r="G200" s="4">
         <v>1.2</v>
       </c>
     </row>
@@ -5038,7 +5095,7 @@
       <c r="C201">
         <v>0.42700476199999998</v>
       </c>
-      <c r="D201" s="4">
+      <c r="D201" s="3">
         <v>59812</v>
       </c>
       <c r="E201" s="3">
@@ -5047,7 +5104,7 @@
       <c r="F201">
         <v>85.1</v>
       </c>
-      <c r="G201" s="5">
+      <c r="G201" s="4">
         <v>0.8</v>
       </c>
     </row>
@@ -5061,7 +5118,7 @@
       <c r="C202">
         <v>0.42987142900000003</v>
       </c>
-      <c r="D202" s="4">
+      <c r="D202" s="3">
         <v>61090</v>
       </c>
       <c r="E202" s="3">
@@ -5070,7 +5127,7 @@
       <c r="F202">
         <v>85.2</v>
       </c>
-      <c r="G202" s="5">
+      <c r="G202" s="4">
         <v>0.7</v>
       </c>
     </row>
@@ -5084,7 +5141,7 @@
       <c r="C203">
         <v>0.43131304300000001</v>
       </c>
-      <c r="D203" s="4">
+      <c r="D203" s="3">
         <v>62045</v>
       </c>
       <c r="E203" s="3">
@@ -5093,7 +5150,7 @@
       <c r="F203">
         <v>85.7</v>
       </c>
-      <c r="G203" s="5">
+      <c r="G203" s="4">
         <v>0.8</v>
       </c>
     </row>
@@ -5107,7 +5164,7 @@
       <c r="C204">
         <v>0.42996666700000002</v>
       </c>
-      <c r="D204" s="4">
+      <c r="D204" s="3">
         <v>61892</v>
       </c>
       <c r="E204" s="3">
@@ -5116,7 +5173,7 @@
       <c r="F204">
         <v>85.7</v>
       </c>
-      <c r="G204" s="5">
+      <c r="G204" s="4">
         <v>0.8</v>
       </c>
     </row>
@@ -5130,7 +5187,7 @@
       <c r="C205">
         <v>0.42145500000000002</v>
       </c>
-      <c r="D205" s="4">
+      <c r="D205" s="3">
         <v>59569</v>
       </c>
       <c r="E205" s="3">
@@ -5139,7 +5196,7 @@
       <c r="F205">
         <v>85.4</v>
       </c>
-      <c r="G205" s="5">
+      <c r="G205" s="4">
         <v>1</v>
       </c>
     </row>
@@ -5153,7 +5210,7 @@
       <c r="C206">
         <v>0.42870909099999999</v>
       </c>
-      <c r="D206" s="4">
+      <c r="D206" s="3">
         <v>61499</v>
       </c>
       <c r="E206" s="3">
@@ -5162,7 +5219,7 @@
       <c r="F206">
         <v>85.9</v>
       </c>
-      <c r="G206" s="5">
+      <c r="G206" s="4">
         <v>1.2</v>
       </c>
     </row>
@@ -5176,7 +5233,7 @@
       <c r="C207">
         <v>0.419655</v>
       </c>
-      <c r="D207" s="4">
+      <c r="D207" s="3">
         <v>60792</v>
       </c>
       <c r="E207" s="3">
@@ -5185,7 +5242,7 @@
       <c r="F207">
         <v>86.4</v>
       </c>
-      <c r="G207" s="5">
+      <c r="G207" s="4">
         <v>1.7</v>
       </c>
     </row>
@@ -5199,7 +5256,7 @@
       <c r="C208">
         <v>0.41588095200000003</v>
       </c>
-      <c r="D208" s="4">
+      <c r="D208" s="3">
         <v>60768</v>
       </c>
       <c r="E208" s="3">
@@ -5208,7 +5265,7 @@
       <c r="F208">
         <v>86.8</v>
       </c>
-      <c r="G208" s="5">
+      <c r="G208" s="4">
         <v>1.8</v>
       </c>
     </row>
@@ -5222,7 +5279,7 @@
       <c r="C209">
         <v>0.42196</v>
       </c>
-      <c r="D209" s="4">
+      <c r="D209" s="3">
         <v>61024</v>
       </c>
       <c r="E209" s="3">
@@ -5231,7 +5288,7 @@
       <c r="F209">
         <v>86.9</v>
       </c>
-      <c r="G209" s="5">
+      <c r="G209" s="4">
         <v>0.6</v>
       </c>
     </row>
@@ -5245,7 +5302,7 @@
       <c r="C210">
         <v>0.42334500000000003</v>
       </c>
-      <c r="D210" s="4">
+      <c r="D210" s="3">
         <v>61603</v>
       </c>
       <c r="E210" s="3">
@@ -5254,7 +5311,7 @@
       <c r="F210">
         <v>87.1</v>
       </c>
-      <c r="G210" s="5">
+      <c r="G210" s="4">
         <v>0</v>
       </c>
     </row>
@@ -5268,7 +5325,7 @@
       <c r="C211">
         <v>0.42509047599999999</v>
       </c>
-      <c r="D211" s="4">
+      <c r="D211" s="3">
         <v>60772</v>
       </c>
       <c r="E211" s="3">
@@ -5277,7 +5334,7 @@
       <c r="F211">
         <v>87.5</v>
       </c>
-      <c r="G211" s="5">
+      <c r="G211" s="4">
         <v>-0.3</v>
       </c>
     </row>
@@ -5291,7 +5348,7 @@
       <c r="C212">
         <v>0.42829130399999998</v>
       </c>
-      <c r="D212" s="4">
+      <c r="D212" s="3">
         <v>64163</v>
       </c>
       <c r="E212" s="3">
@@ -5300,7 +5357,7 @@
       <c r="F212">
         <v>87.9</v>
       </c>
-      <c r="G212" s="5">
+      <c r="G212" s="4">
         <v>0.5</v>
       </c>
     </row>
@@ -5314,7 +5371,7 @@
       <c r="C213">
         <v>0.42281000000000002</v>
       </c>
-      <c r="D213" s="4">
+      <c r="D213" s="3">
         <v>61569</v>
       </c>
       <c r="E213" s="3">
@@ -5323,7 +5380,7 @@
       <c r="F213">
         <v>87.9</v>
       </c>
-      <c r="G213" s="5">
+      <c r="G213" s="4">
         <v>0.6</v>
       </c>
     </row>
@@ -5337,7 +5394,7 @@
       <c r="C214">
         <v>0.43185454499999998</v>
       </c>
-      <c r="D214" s="4">
+      <c r="D214" s="3">
         <v>62583</v>
       </c>
       <c r="E214" s="3">
@@ -5346,7 +5403,7 @@
       <c r="F214">
         <v>88.1</v>
       </c>
-      <c r="G214" s="5">
+      <c r="G214" s="4">
         <v>0.9</v>
       </c>
     </row>
@@ -5360,7 +5417,7 @@
       <c r="C215">
         <v>0.43080000000000002</v>
       </c>
-      <c r="D215" s="4">
+      <c r="D215" s="3">
         <v>64173</v>
       </c>
       <c r="E215" s="3">
@@ -5369,7 +5426,7 @@
       <c r="F215">
         <v>88.5</v>
       </c>
-      <c r="G215" s="5">
+      <c r="G215" s="4">
         <v>1.4</v>
       </c>
     </row>
@@ -5383,7 +5440,7 @@
       <c r="C216">
         <v>0.43247000000000002</v>
       </c>
-      <c r="D216" s="4">
+      <c r="D216" s="3">
         <v>65960</v>
       </c>
       <c r="E216" s="3">
@@ -5392,7 +5449,7 @@
       <c r="F216">
         <v>88.4</v>
       </c>
-      <c r="G216" s="5">
+      <c r="G216" s="4">
         <v>1.7</v>
       </c>
     </row>
@@ -5406,7 +5463,7 @@
       <c r="C217">
         <v>0.42799999999999999</v>
       </c>
-      <c r="D217" s="4">
+      <c r="D217" s="3">
         <v>70299</v>
       </c>
       <c r="E217" s="3">
@@ -5415,7 +5472,7 @@
       <c r="F217">
         <v>88.5</v>
       </c>
-      <c r="G217" s="5">
+      <c r="G217" s="4">
         <v>2</v>
       </c>
     </row>
@@ -5429,7 +5486,7 @@
       <c r="C218">
         <v>0.43548571400000002</v>
       </c>
-      <c r="D218" s="4">
+      <c r="D218" s="3">
         <v>66950</v>
       </c>
       <c r="E218" s="3">
@@ -5438,7 +5495,7 @@
       <c r="F218">
         <v>88.4</v>
       </c>
-      <c r="G218" s="5">
+      <c r="G218" s="4">
         <v>1.8</v>
       </c>
     </row>
@@ -5452,7 +5509,7 @@
       <c r="C219">
         <v>0.45111499999999999</v>
       </c>
-      <c r="D219" s="4">
+      <c r="D219" s="3">
         <v>66531</v>
       </c>
       <c r="E219" s="3">
@@ -5461,7 +5518,7 @@
       <c r="F219">
         <v>88.7</v>
       </c>
-      <c r="G219" s="5">
+      <c r="G219" s="4">
         <v>1.7</v>
       </c>
     </row>
@@ -5475,7 +5532,7 @@
       <c r="C220">
         <v>0.45679999999999998</v>
       </c>
-      <c r="D220" s="4">
+      <c r="D220" s="3">
         <v>65554</v>
       </c>
       <c r="E220" s="3">
@@ -5484,7 +5541,7 @@
       <c r="F220">
         <v>88.8</v>
       </c>
-      <c r="G220" s="5">
+      <c r="G220" s="4">
         <v>2.2999999999999998</v>
       </c>
     </row>
@@ -5498,7 +5555,7 @@
       <c r="C221">
         <v>0.45740500000000001</v>
       </c>
-      <c r="D221" s="4">
+      <c r="D221" s="3">
         <v>65436</v>
       </c>
       <c r="E221" s="3">
@@ -5507,7 +5564,7 @@
       <c r="F221">
         <v>89</v>
       </c>
-      <c r="G221" s="5">
+      <c r="G221" s="4">
         <v>2.7</v>
       </c>
     </row>
@@ -5521,7 +5578,7 @@
       <c r="C222">
         <v>0.46195263199999997</v>
       </c>
-      <c r="D222" s="4">
+      <c r="D222" s="3">
         <v>65164</v>
       </c>
       <c r="E222" s="3">
@@ -5530,7 +5587,7 @@
       <c r="F222">
         <v>89</v>
       </c>
-      <c r="G222" s="5">
+      <c r="G222" s="4">
         <v>3.1</v>
       </c>
     </row>
@@ -5544,7 +5601,7 @@
       <c r="C223">
         <v>0.45664090899999998</v>
       </c>
-      <c r="D223" s="4">
+      <c r="D223" s="3">
         <v>65335</v>
       </c>
       <c r="E223" s="3">
@@ -5553,7 +5610,7 @@
       <c r="F223">
         <v>88.9</v>
       </c>
-      <c r="G223" s="5">
+      <c r="G223" s="4">
         <v>2.5</v>
       </c>
     </row>
@@ -5567,7 +5624,7 @@
       <c r="C224">
         <v>0.45486086999999997</v>
       </c>
-      <c r="D224" s="4">
+      <c r="D224" s="3">
         <v>65308</v>
       </c>
       <c r="E224" s="3">
@@ -5576,7 +5633,7 @@
       <c r="F224">
         <v>89.3</v>
       </c>
-      <c r="G224" s="5">
+      <c r="G224" s="4">
         <v>2.8</v>
       </c>
     </row>
@@ -5590,7 +5647,7 @@
       <c r="C225">
         <v>0.45899000000000001</v>
       </c>
-      <c r="D225" s="4">
+      <c r="D225" s="3">
         <v>64343</v>
       </c>
       <c r="E225" s="3">
@@ -5599,7 +5656,7 @@
       <c r="F225">
         <v>89.2</v>
       </c>
-      <c r="G225" s="5">
+      <c r="G225" s="4">
         <v>3</v>
       </c>
     </row>
@@ -5613,7 +5670,7 @@
       <c r="C226">
         <v>0.45436818200000001</v>
       </c>
-      <c r="D226" s="4">
+      <c r="D226" s="3">
         <v>65061</v>
       </c>
       <c r="E226" s="3">
@@ -5622,7 +5679,7 @@
       <c r="F226">
         <v>89.3</v>
       </c>
-      <c r="G226" s="5">
+      <c r="G226" s="4">
         <v>2.9</v>
       </c>
     </row>
@@ -5636,7 +5693,7 @@
       <c r="C227">
         <v>0.46215909100000002</v>
       </c>
-      <c r="D227" s="4">
+      <c r="D227" s="3">
         <v>68701</v>
       </c>
       <c r="E227" s="3">
@@ -5645,7 +5702,7 @@
       <c r="F227">
         <v>89.7</v>
       </c>
-      <c r="G227" s="5">
+      <c r="G227" s="4">
         <v>2.4</v>
       </c>
     </row>
@@ -5659,7 +5716,7 @@
       <c r="C228">
         <v>0.463561905</v>
       </c>
-      <c r="D228" s="4">
+      <c r="D228" s="3">
         <v>67596</v>
       </c>
       <c r="E228" s="3">
@@ -5668,7 +5725,7 @@
       <c r="F228">
         <v>89.6</v>
       </c>
-      <c r="G228" s="5">
+      <c r="G228" s="4">
         <v>2</v>
       </c>
     </row>
@@ -5682,7 +5739,7 @@
       <c r="C229">
         <v>0.457461905</v>
       </c>
-      <c r="D229" s="4">
+      <c r="D229" s="3">
         <v>66471</v>
       </c>
       <c r="E229" s="3">
@@ -5691,7 +5748,7 @@
       <c r="F229">
         <v>89.9</v>
       </c>
-      <c r="G229" s="5">
+      <c r="G229" s="4">
         <v>1.9</v>
       </c>
     </row>
@@ -5705,7 +5762,7 @@
       <c r="C230">
         <v>0.46585500000000002</v>
       </c>
-      <c r="D230" s="4">
+      <c r="D230" s="3">
         <v>65958</v>
       </c>
       <c r="E230" s="3">
@@ -5714,7 +5771,7 @@
       <c r="F230">
         <v>90</v>
       </c>
-      <c r="G230" s="5">
+      <c r="G230" s="4">
         <v>2.2000000000000002</v>
       </c>
     </row>
@@ -5728,7 +5785,7 @@
       <c r="C231">
         <v>0.465652381</v>
       </c>
-      <c r="D231" s="4">
+      <c r="D231" s="3">
         <v>68781</v>
       </c>
       <c r="E231" s="3">
@@ -5737,7 +5794,7 @@
       <c r="F231">
         <v>90.5</v>
       </c>
-      <c r="G231" s="5">
+      <c r="G231" s="4">
         <v>2</v>
       </c>
     </row>
@@ -5751,7 +5808,7 @@
       <c r="C232">
         <v>0.46461428599999999</v>
       </c>
-      <c r="D232" s="4">
+      <c r="D232" s="3">
         <v>69068</v>
       </c>
       <c r="E232" s="3">
@@ -5760,7 +5817,7 @@
       <c r="F232">
         <v>90.3</v>
       </c>
-      <c r="G232" s="5">
+      <c r="G232" s="4">
         <v>2.1</v>
       </c>
     </row>
@@ -5774,7 +5831,7 @@
       <c r="C233">
         <v>0.46632857100000003</v>
       </c>
-      <c r="D233" s="4">
+      <c r="D233" s="3">
         <v>69919</v>
       </c>
       <c r="E233" s="3">
@@ -5783,7 +5840,7 @@
       <c r="F233">
         <v>91.2</v>
       </c>
-      <c r="G233" s="5">
+      <c r="G233" s="4">
         <v>2.2000000000000002</v>
       </c>
     </row>
@@ -5797,7 +5854,7 @@
       <c r="C234">
         <v>0.46330500000000002</v>
       </c>
-      <c r="D234" s="4">
+      <c r="D234" s="3">
         <v>66753</v>
       </c>
       <c r="E234" s="3">
@@ -5806,7 +5863,7 @@
       <c r="F234">
         <v>90.9</v>
       </c>
-      <c r="G234" s="5">
+      <c r="G234" s="4">
         <v>2.4</v>
       </c>
     </row>
@@ -5820,7 +5877,7 @@
       <c r="C235">
         <v>0.45975909100000001</v>
       </c>
-      <c r="D235" s="4">
+      <c r="D235" s="3">
         <v>68724</v>
       </c>
       <c r="E235" s="3">
@@ -5829,7 +5886,7 @@
       <c r="F235">
         <v>91.1</v>
       </c>
-      <c r="G235" s="5">
+      <c r="G235" s="4">
         <v>2.6</v>
       </c>
     </row>
@@ -5843,7 +5900,7 @@
       <c r="C236">
         <v>0.4577</v>
       </c>
-      <c r="D236" s="4">
+      <c r="D236" s="3">
         <v>69478</v>
       </c>
       <c r="E236" s="3">
@@ -5852,7 +5909,7 @@
       <c r="F236">
         <v>91.2</v>
       </c>
-      <c r="G236" s="5">
+      <c r="G236" s="4">
         <v>2.5</v>
       </c>
     </row>
@@ -5866,7 +5923,7 @@
       <c r="C237">
         <v>0.247772727</v>
       </c>
-      <c r="D237" s="4">
+      <c r="D237" s="3">
         <v>72101</v>
       </c>
       <c r="E237" s="3">
@@ -5875,7 +5932,7 @@
       <c r="F237">
         <v>91.4</v>
       </c>
-      <c r="G237" s="5">
+      <c r="G237" s="4">
         <v>2.4</v>
       </c>
     </row>
@@ -5889,7 +5946,7 @@
       <c r="C238">
         <v>0.21302727299999999</v>
       </c>
-      <c r="D238" s="4">
+      <c r="D238" s="3">
         <v>70798</v>
       </c>
       <c r="E238" s="3">
@@ -5898,7 +5955,7 @@
       <c r="F238">
         <v>91.9</v>
       </c>
-      <c r="G238" s="5">
+      <c r="G238" s="4">
         <v>2.4</v>
       </c>
     </row>
@@ -5912,7 +5969,7 @@
       <c r="C239">
         <v>0.212028571</v>
       </c>
-      <c r="D239" s="4">
+      <c r="D239" s="3">
         <v>66977</v>
       </c>
       <c r="E239" s="3">
@@ -5921,7 +5978,7 @@
       <c r="F239">
         <v>91.6</v>
       </c>
-      <c r="G239" s="5">
+      <c r="G239" s="4">
         <v>2.5</v>
       </c>
     </row>
@@ -5935,7 +5992,7 @@
       <c r="C240">
         <v>0.21084545499999999</v>
       </c>
-      <c r="D240" s="4">
+      <c r="D240" s="3">
         <v>69431</v>
       </c>
       <c r="E240" s="3">
@@ -5944,7 +6001,7 @@
       <c r="F240">
         <v>92.1</v>
       </c>
-      <c r="G240" s="5">
+      <c r="G240" s="4">
         <v>2.7</v>
       </c>
     </row>
@@ -5958,7 +6015,7 @@
       <c r="C241">
         <v>0.21249499999999999</v>
       </c>
-      <c r="D241" s="4">
+      <c r="D241" s="3">
         <v>69969</v>
       </c>
       <c r="E241" s="3">
@@ -5967,7 +6024,7 @@
       <c r="F241">
         <v>92.8</v>
       </c>
-      <c r="G241" s="5">
+      <c r="G241" s="4">
         <v>2.5</v>
       </c>
     </row>
@@ -5981,7 +6038,7 @@
       <c r="C242">
         <v>0.21350952400000001</v>
       </c>
-      <c r="D242" s="4">
+      <c r="D242" s="3">
         <v>68987</v>
       </c>
       <c r="E242" s="3">
@@ -5990,7 +6047,7 @@
       <c r="F242">
         <v>93</v>
       </c>
-      <c r="G242" s="5">
+      <c r="G242" s="4">
         <v>2.1</v>
       </c>
     </row>
@@ -6004,7 +6061,7 @@
       <c r="C243">
         <v>0.210645</v>
       </c>
-      <c r="D243" s="4">
+      <c r="D243" s="3">
         <v>68699</v>
       </c>
       <c r="E243" s="3">
@@ -6013,7 +6070,7 @@
       <c r="F243">
         <v>93.1</v>
       </c>
-      <c r="G243" s="5">
+      <c r="G243" s="4">
         <v>2.1</v>
       </c>
     </row>
@@ -6027,7 +6084,7 @@
       <c r="C244">
         <v>0.20953912999999999</v>
       </c>
-      <c r="D244" s="4">
+      <c r="D244" s="3">
         <v>71082</v>
       </c>
       <c r="E244" s="3">
@@ -6036,7 +6093,7 @@
       <c r="F244">
         <v>93.2</v>
       </c>
-      <c r="G244" s="5">
+      <c r="G244" s="4">
         <v>2.2999999999999998</v>
       </c>
     </row>
@@ -6050,7 +6107,7 @@
       <c r="C245">
         <v>0.21135000000000001</v>
       </c>
-      <c r="D245" s="4">
+      <c r="D245" s="3">
         <v>70487</v>
       </c>
       <c r="E245" s="3">
@@ -6059,7 +6116,7 @@
       <c r="F245">
         <v>93.6</v>
       </c>
-      <c r="G245" s="5">
+      <c r="G245" s="4">
         <v>2.2000000000000002</v>
       </c>
     </row>
@@ -6073,7 +6130,7 @@
       <c r="C246">
         <v>0.21263333300000001</v>
       </c>
-      <c r="D246" s="4">
+      <c r="D246" s="3">
         <v>71313</v>
       </c>
       <c r="E246" s="3">
@@ -6082,7 +6139,7 @@
       <c r="F246">
         <v>93.9</v>
       </c>
-      <c r="G246" s="5">
+      <c r="G246" s="4">
         <v>1.9</v>
       </c>
     </row>
@@ -6096,7 +6153,7 @@
       <c r="C247">
         <v>0.21207272699999999</v>
       </c>
-      <c r="D247" s="4">
+      <c r="D247" s="3">
         <v>73483</v>
       </c>
       <c r="E247" s="3">
@@ -6105,7 +6162,7 @@
       <c r="F247">
         <v>94.1</v>
       </c>
-      <c r="G247" s="5">
+      <c r="G247" s="4">
         <v>2.2000000000000002</v>
       </c>
     </row>
@@ -6119,7 +6176,7 @@
       <c r="C248">
         <v>0.21236666700000001</v>
       </c>
-      <c r="D248" s="4">
+      <c r="D248" s="3">
         <v>72404</v>
       </c>
       <c r="E248" s="3">
@@ -6128,7 +6185,7 @@
       <c r="F248">
         <v>94.2</v>
       </c>
-      <c r="G248" s="5">
+      <c r="G248" s="4">
         <v>2.2000000000000002</v>
       </c>
     </row>
@@ -6142,7 +6199,7 @@
       <c r="C249">
         <v>0.213154545</v>
       </c>
-      <c r="D249" s="4">
+      <c r="D249" s="3">
         <v>71896</v>
       </c>
       <c r="E249" s="3">
@@ -6151,7 +6208,7 @@
       <c r="F249">
         <v>94.4</v>
       </c>
-      <c r="G249" s="5">
+      <c r="G249" s="4">
         <v>2.4</v>
       </c>
     </row>
@@ -6165,7 +6222,7 @@
       <c r="C250">
         <v>0.212342857</v>
       </c>
-      <c r="D250" s="4">
+      <c r="D250" s="3">
         <v>72226</v>
       </c>
       <c r="E250" s="3">
@@ -6174,7 +6231,7 @@
       <c r="F250">
         <v>94.8</v>
       </c>
-      <c r="G250" s="5">
+      <c r="G250" s="4">
         <v>2.2999999999999998</v>
       </c>
     </row>
@@ -6188,7 +6245,7 @@
       <c r="C251">
         <v>0.210972727</v>
       </c>
-      <c r="D251" s="4">
+      <c r="D251" s="3">
         <v>70570</v>
       </c>
       <c r="E251" s="3">
@@ -6197,7 +6254,7 @@
       <c r="F251">
         <v>94.9</v>
       </c>
-      <c r="G251" s="5">
+      <c r="G251" s="4">
         <v>2.6</v>
       </c>
     </row>
@@ -6211,7 +6268,7 @@
       <c r="C252">
         <v>0.44927272699999998</v>
       </c>
-      <c r="D252" s="4">
+      <c r="D252" s="3">
         <v>71580</v>
       </c>
       <c r="E252" s="3">
@@ -6220,7 +6277,7 @@
       <c r="F252">
         <v>95.1</v>
       </c>
-      <c r="G252" s="5">
+      <c r="G252" s="4">
         <v>2.5</v>
       </c>
     </row>
@@ -6234,7 +6291,7 @@
       <c r="C253">
         <v>0.46191578900000002</v>
       </c>
-      <c r="D253" s="4">
+      <c r="D253" s="3">
         <v>70578</v>
       </c>
       <c r="E253" s="3">
@@ -6243,7 +6300,7 @@
       <c r="F253">
         <v>95.3</v>
       </c>
-      <c r="G253" s="5">
+      <c r="G253" s="4">
         <v>2.6</v>
       </c>
     </row>
@@ -6257,7 +6314,7 @@
       <c r="C254">
         <v>0.46312272700000001</v>
       </c>
-      <c r="D254" s="4">
+      <c r="D254" s="3">
         <v>73395</v>
       </c>
       <c r="E254" s="3">
@@ -6266,7 +6323,7 @@
       <c r="F254">
         <v>95.2</v>
       </c>
-      <c r="G254" s="5">
+      <c r="G254" s="4">
         <v>2.7</v>
       </c>
     </row>
@@ -6280,7 +6337,7 @@
       <c r="C255">
         <v>0.46340999999999999</v>
       </c>
-      <c r="D255" s="4">
+      <c r="D255" s="3">
         <v>69341</v>
       </c>
       <c r="E255" s="3">
@@ -6289,7 +6346,7 @@
       <c r="F255">
         <v>95.2</v>
       </c>
-      <c r="G255" s="5">
+      <c r="G255" s="4">
         <v>2.9</v>
       </c>
     </row>
@@ -6303,7 +6360,7 @@
       <c r="C256">
         <v>0.46370952399999998</v>
       </c>
-      <c r="D256" s="4">
+      <c r="D256" s="3">
         <v>72928</v>
       </c>
       <c r="E256" s="3">
@@ -6312,7 +6369,7 @@
       <c r="F256">
         <v>95.1</v>
       </c>
-      <c r="G256" s="5">
+      <c r="G256" s="4">
         <v>2.6</v>
       </c>
     </row>
@@ -6326,7 +6383,7 @@
       <c r="C257">
         <v>0.46169500000000002</v>
       </c>
-      <c r="D257" s="4">
+      <c r="D257" s="3">
         <v>73963</v>
       </c>
       <c r="E257" s="3">
@@ -6335,7 +6392,7 @@
       <c r="F257">
         <v>95.1</v>
       </c>
-      <c r="G257" s="5">
+      <c r="G257" s="4">
         <v>2.6</v>
       </c>
     </row>
@@ -6349,7 +6406,7 @@
       <c r="C258">
         <v>0.45286190500000001</v>
       </c>
-      <c r="D258" s="4">
+      <c r="D258" s="3">
         <v>73371</v>
       </c>
       <c r="E258" s="3">
@@ -6358,7 +6415,7 @@
       <c r="F258">
         <v>95.4</v>
       </c>
-      <c r="G258" s="5">
+      <c r="G258" s="4">
         <v>2.5</v>
       </c>
     </row>
@@ -6372,7 +6429,7 @@
       <c r="C259">
         <v>0.45065238099999999</v>
       </c>
-      <c r="D259" s="4">
+      <c r="D259" s="3">
         <v>72174</v>
       </c>
       <c r="E259" s="3">
@@ -6381,7 +6438,7 @@
       <c r="F259">
         <v>95.7</v>
       </c>
-      <c r="G259" s="5">
+      <c r="G259" s="4">
         <v>2.4</v>
       </c>
     </row>
@@ -6395,7 +6452,7 @@
       <c r="C260">
         <v>0.45453181799999998</v>
       </c>
-      <c r="D260" s="4">
+      <c r="D260" s="3">
         <v>73095</v>
       </c>
       <c r="E260" s="3">
@@ -6404,7 +6461,7 @@
       <c r="F260">
         <v>95.5</v>
       </c>
-      <c r="G260" s="5">
+      <c r="G260" s="4">
         <v>2.7</v>
       </c>
     </row>
@@ -6418,7 +6475,7 @@
       <c r="C261">
         <v>0.69105000000000005</v>
       </c>
-      <c r="D261" s="4">
+      <c r="D261" s="3">
         <v>73914</v>
       </c>
       <c r="E261" s="3">
@@ -6427,7 +6484,7 @@
       <c r="F261">
         <v>95.8</v>
       </c>
-      <c r="G261" s="5">
+      <c r="G261" s="4">
         <v>2.9</v>
       </c>
     </row>
@@ -6441,7 +6498,7 @@
       <c r="C262">
         <v>0.70120499999999997</v>
       </c>
-      <c r="D262" s="4">
+      <c r="D262" s="3">
         <v>72692</v>
       </c>
       <c r="E262" s="3">
@@ -6450,7 +6507,7 @@
       <c r="F262">
         <v>95.9</v>
       </c>
-      <c r="G262" s="5">
+      <c r="G262" s="4">
         <v>3.1</v>
       </c>
     </row>
@@ -6464,7 +6521,7 @@
       <c r="C263">
         <v>0.70108260899999997</v>
       </c>
-      <c r="D263" s="4">
+      <c r="D263" s="3">
         <v>76367</v>
       </c>
       <c r="E263" s="3">
@@ -6473,7 +6530,7 @@
       <c r="F263">
         <v>95.9</v>
       </c>
-      <c r="G263" s="5">
+      <c r="G263" s="4">
         <v>3.4</v>
       </c>
     </row>
@@ -6487,7 +6544,7 @@
       <c r="C264">
         <v>0.70169545499999997</v>
       </c>
-      <c r="D264" s="4">
+      <c r="D264" s="3">
         <v>76190</v>
       </c>
       <c r="E264" s="3">
@@ -6496,7 +6553,7 @@
       <c r="F264">
         <v>96</v>
       </c>
-      <c r="G264" s="5">
+      <c r="G264" s="4">
         <v>3.4</v>
       </c>
     </row>
@@ -6510,7 +6567,7 @@
       <c r="C265">
         <v>0.70261578899999999</v>
       </c>
-      <c r="D265" s="4">
+      <c r="D265" s="3">
         <v>74994</v>
       </c>
       <c r="E265" s="3">
@@ -6519,7 +6576,7 @@
       <c r="F265">
         <v>95.5</v>
       </c>
-      <c r="G265" s="5">
+      <c r="G265" s="4">
         <v>3.5</v>
       </c>
     </row>
@@ -6533,7 +6590,7 @@
       <c r="C266">
         <v>0.70525454499999995</v>
       </c>
-      <c r="D266" s="4">
+      <c r="D266" s="3">
         <v>81058</v>
       </c>
       <c r="E266" s="3">
@@ -6542,7 +6599,7 @@
       <c r="F266">
         <v>96</v>
       </c>
-      <c r="G266" s="5">
+      <c r="G266" s="4">
         <v>3.4</v>
       </c>
     </row>
@@ -6556,7 +6613,7 @@
       <c r="C267">
         <v>0.70614500000000002</v>
       </c>
-      <c r="D267" s="4">
+      <c r="D267" s="3">
         <v>81769</v>
       </c>
       <c r="E267" s="3">
@@ -6565,7 +6622,7 @@
       <c r="F267">
         <v>96.5</v>
       </c>
-      <c r="G267" s="5">
+      <c r="G267" s="4">
         <v>3.6</v>
       </c>
     </row>
@@ -6579,7 +6636,7 @@
       <c r="C268">
         <v>0.70528571399999995</v>
       </c>
-      <c r="D268" s="4">
+      <c r="D268" s="3">
         <v>83150</v>
       </c>
       <c r="E268" s="3">
@@ -6588,7 +6645,7 @@
       <c r="F268">
         <v>96.4</v>
       </c>
-      <c r="G268" s="5">
+      <c r="G268" s="4">
         <v>3.3</v>
       </c>
     </row>
@@ -6602,7 +6659,7 @@
       <c r="C269">
         <v>0.70810499999999998</v>
       </c>
-      <c r="D269" s="4">
+      <c r="D269" s="3">
         <v>74659</v>
       </c>
       <c r="E269" s="3">
@@ -6611,7 +6668,7 @@
       <c r="F269">
         <v>96</v>
       </c>
-      <c r="G269" s="5">
+      <c r="G269" s="4">
         <v>3.2</v>
       </c>
     </row>
@@ -6625,7 +6682,7 @@
       <c r="C270">
         <v>0.70940476200000002</v>
       </c>
-      <c r="D270" s="4">
+      <c r="D270" s="3">
         <v>73965</v>
       </c>
       <c r="E270" s="3">
@@ -6634,7 +6691,7 @@
       <c r="F270">
         <v>96.5</v>
       </c>
-      <c r="G270" s="5">
+      <c r="G270" s="4">
         <v>3.4</v>
       </c>
     </row>
@@ -6648,7 +6705,7 @@
       <c r="C271">
         <v>0.70853500000000003</v>
       </c>
-      <c r="D271" s="4">
+      <c r="D271" s="3">
         <v>72862</v>
       </c>
       <c r="E271" s="3">
@@ -6657,7 +6714,7 @@
       <c r="F271">
         <v>97.1</v>
       </c>
-      <c r="G271" s="5">
+      <c r="G271" s="4">
         <v>3.9</v>
       </c>
     </row>
@@ -6671,7 +6728,7 @@
       <c r="C272">
         <v>0.70899999999999996</v>
       </c>
-      <c r="D272" s="4">
+      <c r="D272" s="3">
         <v>74107</v>
       </c>
       <c r="E272" s="3">
@@ -6680,7 +6737,7 @@
       <c r="F272">
         <v>97.2</v>
       </c>
-      <c r="G272" s="5">
+      <c r="G272" s="4">
         <v>4</v>
       </c>
     </row>
@@ -6694,7 +6751,7 @@
       <c r="C273">
         <v>0.71009523799999996</v>
       </c>
-      <c r="D273" s="4">
+      <c r="D273" s="3">
         <v>75208</v>
       </c>
       <c r="E273" s="3">
@@ -6703,7 +6760,7 @@
       <c r="F273">
         <v>97</v>
       </c>
-      <c r="G273" s="5">
+      <c r="G273" s="4">
         <v>3.8</v>
       </c>
     </row>
@@ -6717,7 +6774,7 @@
       <c r="C274">
         <v>0.70982857099999996</v>
       </c>
-      <c r="D274" s="4">
+      <c r="D274" s="3">
         <v>75192</v>
       </c>
       <c r="E274" s="3">
@@ -6726,7 +6783,7 @@
       <c r="F274">
         <v>97.4</v>
       </c>
-      <c r="G274" s="5">
+      <c r="G274" s="4">
         <v>3.8</v>
       </c>
     </row>
@@ -6740,7 +6797,7 @@
       <c r="C275">
         <v>0.71083043499999998</v>
       </c>
-      <c r="D275" s="4">
+      <c r="D275" s="3">
         <v>77142</v>
       </c>
       <c r="E275" s="3">
@@ -6749,7 +6806,7 @@
       <c r="F275">
         <v>97.3</v>
       </c>
-      <c r="G275" s="5">
+      <c r="G275" s="4">
         <v>3.2</v>
       </c>
     </row>
@@ -6763,7 +6820,7 @@
       <c r="C276">
         <v>0.71052380999999998</v>
       </c>
-      <c r="D276" s="4">
+      <c r="D276" s="3">
         <v>70394</v>
       </c>
       <c r="E276" s="3">
@@ -6772,7 +6829,7 @@
       <c r="F276">
         <v>97</v>
       </c>
-      <c r="G276" s="5">
+      <c r="G276" s="4">
         <v>3.2</v>
       </c>
     </row>
@@ -6786,7 +6843,7 @@
       <c r="C277">
         <v>0.71006499999999995</v>
       </c>
-      <c r="D277" s="4">
+      <c r="D277" s="3">
         <v>70119</v>
       </c>
       <c r="E277" s="3">
@@ -6795,7 +6852,7 @@
       <c r="F277">
         <v>97.4</v>
       </c>
-      <c r="G277" s="5">
+      <c r="G277" s="4">
         <v>2.7</v>
       </c>
     </row>
@@ -6809,7 +6866,7 @@
       <c r="C278">
         <v>0.71130909099999995</v>
       </c>
-      <c r="D278" s="4">
+      <c r="D278" s="3">
         <v>72716</v>
       </c>
       <c r="E278" s="3">
@@ -6818,7 +6875,7 @@
       <c r="F278">
         <v>97.3</v>
       </c>
-      <c r="G278" s="5">
+      <c r="G278" s="4">
         <v>3</v>
       </c>
     </row>
@@ -6832,7 +6889,7 @@
       <c r="C279">
         <v>0.71038000000000001</v>
       </c>
-      <c r="D279" s="4">
+      <c r="D279" s="3">
         <v>72985</v>
       </c>
       <c r="E279" s="3">
@@ -6841,7 +6898,7 @@
       <c r="F279">
         <v>97.3</v>
       </c>
-      <c r="G279" s="5">
+      <c r="G279" s="4">
         <v>2.8</v>
       </c>
     </row>
@@ -6855,7 +6912,7 @@
       <c r="C280">
         <v>0.31924090900000002</v>
       </c>
-      <c r="D280" s="4">
+      <c r="D280" s="3">
         <v>65636</v>
       </c>
       <c r="E280" s="3">
@@ -6864,7 +6921,7 @@
       <c r="F280">
         <v>89.9</v>
       </c>
-      <c r="G280" s="5">
+      <c r="G280" s="4">
         <v>2.2000000000000002</v>
       </c>
     </row>
@@ -6878,7 +6935,7 @@
       <c r="C281">
         <v>6.5875000000000003E-2</v>
       </c>
-      <c r="D281" s="4">
+      <c r="D281" s="3">
         <v>51219</v>
       </c>
       <c r="E281" s="3">
@@ -6887,7 +6944,7 @@
       <c r="F281">
         <v>72.7</v>
       </c>
-      <c r="G281" s="5">
+      <c r="G281" s="4">
         <v>0.9</v>
       </c>
     </row>
@@ -6901,7 +6958,7 @@
       <c r="C282">
         <v>6.7436841999999997E-2</v>
       </c>
-      <c r="D282" s="4">
+      <c r="D282" s="3">
         <v>50286</v>
       </c>
       <c r="E282" s="3">
@@ -6910,7 +6967,7 @@
       <c r="F282">
         <v>74.2</v>
       </c>
-      <c r="G282" s="5">
+      <c r="G282" s="4">
         <v>-0.4</v>
       </c>
     </row>
@@ -6924,7 +6981,7 @@
       <c r="C283">
         <v>6.4604544999999999E-2</v>
       </c>
-      <c r="D283" s="4">
+      <c r="D283" s="3">
         <v>57392</v>
       </c>
       <c r="E283" s="3">
@@ -6933,7 +6990,7 @@
       <c r="F283">
         <v>81.099999999999994</v>
       </c>
-      <c r="G283" s="5">
+      <c r="G283" s="4">
         <v>-1.1000000000000001</v>
       </c>
     </row>
@@ -6947,7 +7004,7 @@
       <c r="C284">
         <v>5.9860869999999997E-2</v>
       </c>
-      <c r="D284" s="4">
+      <c r="D284" s="3">
         <v>60694</v>
       </c>
       <c r="E284" s="3">
@@ -6956,7 +7013,7 @@
       <c r="F284">
         <v>86.6</v>
       </c>
-      <c r="G284" s="5">
+      <c r="G284" s="4">
         <v>-0.9</v>
       </c>
     </row>
@@ -6970,7 +7027,7 @@
       <c r="C285">
         <v>5.6230000000000002E-2</v>
       </c>
-      <c r="D285" s="4">
+      <c r="D285" s="3">
         <v>60754</v>
       </c>
       <c r="E285" s="3">
@@ -6979,7 +7036,7 @@
       <c r="F285">
         <v>89.6</v>
       </c>
-      <c r="G285" s="5">
+      <c r="G285" s="4">
         <v>0.1</v>
       </c>
     </row>
@@ -6993,7 +7050,7 @@
       <c r="C286">
         <v>5.4736364000000003E-2</v>
       </c>
-      <c r="D286" s="4">
+      <c r="D286" s="3">
         <v>65456</v>
       </c>
       <c r="E286" s="3">
@@ -7002,7 +7059,7 @@
       <c r="F286">
         <v>90.8</v>
       </c>
-      <c r="G286" s="5">
+      <c r="G286" s="4">
         <v>1.5</v>
       </c>
     </row>
@@ -7016,7 +7073,7 @@
       <c r="C287">
         <v>5.3845455E-2</v>
       </c>
-      <c r="D287" s="4">
+      <c r="D287" s="3">
         <v>67831</v>
       </c>
       <c r="E287" s="3">
@@ -7025,7 +7082,7 @@
       <c r="F287">
         <v>91.2</v>
       </c>
-      <c r="G287" s="5">
+      <c r="G287" s="4">
         <v>2.8</v>
       </c>
     </row>
@@ -7039,7 +7096,7 @@
       <c r="C288">
         <v>5.3652380999999999E-2</v>
       </c>
-      <c r="D288" s="4">
+      <c r="D288" s="3">
         <v>71662</v>
       </c>
       <c r="E288" s="3">
@@ -7048,7 +7105,7 @@
       <c r="F288">
         <v>89.2</v>
       </c>
-      <c r="G288" s="5">
+      <c r="G288" s="4">
         <v>3.7</v>
       </c>
     </row>
@@ -7062,7 +7119,7 @@
       <c r="C289">
         <v>4.9171429000000003E-2</v>
       </c>
-      <c r="D289" s="4">
+      <c r="D289" s="3">
         <v>74881</v>
       </c>
       <c r="E289" s="3">
@@ -7071,7 +7128,7 @@
       <c r="F289">
         <v>90.8</v>
       </c>
-      <c r="G289" s="5">
+      <c r="G289" s="4">
         <v>4.5999999999999996</v>
       </c>
     </row>
@@ -7085,7 +7142,7 @@
       <c r="C290">
         <v>4.9364999999999999E-2</v>
       </c>
-      <c r="D290" s="4">
+      <c r="D290" s="3">
         <v>64678</v>
       </c>
       <c r="E290" s="3">
@@ -7094,7 +7151,7 @@
       <c r="F290">
         <v>87.8</v>
       </c>
-      <c r="G290" s="5">
+      <c r="G290" s="4">
         <v>4.8</v>
       </c>
     </row>
@@ -7108,7 +7165,7 @@
       <c r="C291">
         <v>4.8625000000000002E-2</v>
       </c>
-      <c r="D291" s="4">
+      <c r="D291" s="3">
         <v>66962</v>
       </c>
       <c r="E291" s="3">
@@ -7117,7 +7174,7 @@
       <c r="F291">
         <v>88.9</v>
       </c>
-      <c r="G291" s="5">
+      <c r="G291" s="4">
         <v>4.5</v>
       </c>
     </row>
@@ -7131,7 +7188,7 @@
       <c r="C292">
         <v>4.8643477999999997E-2</v>
       </c>
-      <c r="D292" s="4">
+      <c r="D292" s="3">
         <v>65976</v>
       </c>
       <c r="E292" s="3">
@@ -7140,7 +7197,7 @@
       <c r="F292">
         <v>91.5</v>
       </c>
-      <c r="G292" s="5">
+      <c r="G292" s="4">
         <v>4.2</v>
       </c>
     </row>
@@ -7154,7 +7211,7 @@
       <c r="C293">
         <v>4.8575E-2</v>
       </c>
-      <c r="D293" s="4">
+      <c r="D293" s="3">
         <v>65113</v>
       </c>
       <c r="E293" s="3">
@@ -7163,7 +7220,7 @@
       <c r="F293">
         <v>94.5</v>
       </c>
-      <c r="G293" s="5">
+      <c r="G293" s="4">
         <v>5.6</v>
       </c>
     </row>
@@ -7177,7 +7234,7 @@
       <c r="C294">
         <v>4.9457895000000002E-2</v>
       </c>
-      <c r="D294" s="4">
+      <c r="D294" s="3">
         <v>65458</v>
       </c>
       <c r="E294" s="3">
@@ -7186,7 +7243,7 @@
       <c r="F294">
         <v>95.8</v>
       </c>
-      <c r="G294" s="5">
+      <c r="G294" s="4">
         <v>7.5</v>
       </c>
     </row>
@@ -7200,7 +7257,7 @@
       <c r="C295">
         <v>4.9840909000000003E-2</v>
       </c>
-      <c r="D295" s="4">
+      <c r="D295" s="3">
         <v>66838</v>
       </c>
       <c r="E295" s="3">
@@ -7209,7 +7266,7 @@
       <c r="F295">
         <v>96.7</v>
       </c>
-      <c r="G295" s="5">
+      <c r="G295" s="4">
         <v>8.9</v>
       </c>
     </row>
@@ -7223,7 +7280,7 @@
       <c r="C296">
         <v>5.0554544999999999E-2</v>
       </c>
-      <c r="D296" s="4">
+      <c r="D296" s="3">
         <v>68424</v>
       </c>
       <c r="E296" s="3">
@@ -7232,7 +7289,7 @@
       <c r="F296">
         <v>96.3</v>
       </c>
-      <c r="G296" s="5">
+      <c r="G296" s="4">
         <v>8.4</v>
       </c>
     </row>
@@ -7246,7 +7303,7 @@
       <c r="C297">
         <v>5.0409523999999997E-2</v>
       </c>
-      <c r="D297" s="4">
+      <c r="D297" s="3">
         <v>67458</v>
       </c>
       <c r="E297" s="3">
@@ -7255,7 +7312,7 @@
       <c r="F297">
         <v>97.3</v>
       </c>
-      <c r="G297" s="5">
+      <c r="G297" s="4">
         <v>7.2</v>
       </c>
     </row>
@@ -7269,7 +7326,7 @@
       <c r="C298">
         <v>4.9950000000000001E-2</v>
       </c>
-      <c r="D298" s="4">
+      <c r="D298" s="3">
         <v>70865</v>
       </c>
       <c r="E298" s="3">
@@ -7278,7 +7335,7 @@
       <c r="F298">
         <v>97.8</v>
       </c>
-      <c r="G298" s="5">
+      <c r="G298" s="4">
         <v>5.9</v>
       </c>
     </row>
@@ -7292,7 +7349,7 @@
       <c r="C299">
         <v>5.0219048000000002E-2</v>
       </c>
-      <c r="D299" s="4">
+      <c r="D299" s="3">
         <v>67833</v>
       </c>
       <c r="E299" s="3">
@@ -7301,7 +7358,7 @@
       <c r="F299">
         <v>98</v>
       </c>
-      <c r="G299" s="5">
+      <c r="G299" s="4">
         <v>5.0999999999999996</v>
       </c>
     </row>
@@ -7315,7 +7372,7 @@
       <c r="C300">
         <v>4.6836363999999998E-2</v>
       </c>
-      <c r="D300" s="4">
+      <c r="D300" s="3">
         <v>70445</v>
       </c>
       <c r="E300" s="3">
@@ -7324,7 +7381,7 @@
       <c r="F300">
         <v>98.5</v>
       </c>
-      <c r="G300" s="5">
+      <c r="G300" s="4">
         <v>4.4000000000000004</v>
       </c>
     </row>
@@ -7338,7 +7395,7 @@
       <c r="C301">
         <v>0.11412381000000001</v>
       </c>
-      <c r="D301" s="4">
+      <c r="D301" s="3">
         <v>72182</v>
       </c>
       <c r="E301" s="3">
@@ -7347,7 +7404,7 @@
       <c r="F301">
         <v>98.3</v>
       </c>
-      <c r="G301" s="5">
+      <c r="G301" s="4">
         <v>4.9000000000000004</v>
       </c>
     </row>
@@ -7361,7 +7418,7 @@
       <c r="C302">
         <v>0.19575999999999999</v>
       </c>
-      <c r="D302" s="4">
+      <c r="D302" s="3">
         <v>78003</v>
       </c>
       <c r="E302" s="3">
@@ -7370,7 +7427,7 @@
       <c r="F302">
         <v>98.9</v>
       </c>
-      <c r="G302" s="5">
+      <c r="G302" s="4">
         <v>5.2</v>
       </c>
     </row>
@@ -7384,7 +7441,7 @@
       <c r="C303">
         <v>0.41988500000000001</v>
       </c>
-      <c r="D303" s="4">
+      <c r="D303" s="3">
         <v>76726</v>
       </c>
       <c r="E303" s="3">
@@ -7393,7 +7450,7 @@
       <c r="F303">
         <v>99.3</v>
       </c>
-      <c r="G303" s="5">
+      <c r="G303" s="4">
         <v>5.9</v>
       </c>
     </row>
@@ -7407,7 +7464,7 @@
       <c r="C304">
         <v>0.56228260900000004</v>
       </c>
-      <c r="D304" s="4">
+      <c r="D304" s="3">
         <v>77619</v>
       </c>
       <c r="E304" s="3">
@@ -7416,7 +7473,7 @@
       <c r="F304">
         <v>99.3</v>
       </c>
-      <c r="G304" s="5">
+      <c r="G304" s="4">
         <v>7.3</v>
       </c>
     </row>
@@ -7430,7 +7487,7 @@
       <c r="C305">
         <v>0.69064210500000001</v>
       </c>
-      <c r="D305" s="4">
+      <c r="D305" s="3">
         <v>77518</v>
       </c>
       <c r="E305" s="3">
@@ -7439,7 +7496,7 @@
       <c r="F305">
         <v>99.5</v>
       </c>
-      <c r="G305" s="5">
+      <c r="G305" s="4">
         <v>7.1</v>
       </c>
     </row>
@@ -7453,7 +7510,7 @@
       <c r="C306">
         <v>0.91578571399999997</v>
       </c>
-      <c r="D306" s="4">
+      <c r="D306" s="3">
         <v>80713</v>
       </c>
       <c r="E306" s="3">
@@ -7462,7 +7519,7 @@
       <c r="F306">
         <v>100</v>
       </c>
-      <c r="G306" s="5">
+      <c r="G306" s="4">
         <v>6.5</v>
       </c>
     </row>
@@ -7476,7 +7533,7 @@
       <c r="C307">
         <v>1.07666</v>
       </c>
-      <c r="D307" s="4">
+      <c r="D307" s="3">
         <v>77362</v>
       </c>
       <c r="E307" s="3">
@@ -7485,7 +7542,7 @@
       <c r="F307">
         <v>99.4</v>
       </c>
-      <c r="G307" s="5">
+      <c r="G307" s="4">
         <v>5.2</v>
       </c>
     </row>
@@ -7499,7 +7556,7 @@
       <c r="C308">
         <v>1.1907904760000001</v>
       </c>
-      <c r="D308" s="4">
+      <c r="D308" s="3">
         <v>75992</v>
       </c>
       <c r="E308" s="3">
@@ -7508,7 +7565,7 @@
       <c r="F308">
         <v>99.9</v>
       </c>
-      <c r="G308" s="5">
+      <c r="G308" s="4">
         <v>5.5</v>
       </c>
     </row>
@@ -7522,7 +7579,7 @@
       <c r="C309">
         <v>1.622004545</v>
       </c>
-      <c r="D309" s="4">
+      <c r="D309" s="3">
         <v>76613</v>
       </c>
       <c r="E309" s="3">
@@ -7531,7 +7588,7 @@
       <c r="F309">
         <v>99.9</v>
       </c>
-      <c r="G309" s="5">
+      <c r="G309" s="4">
         <v>6.1</v>
       </c>
     </row>
@@ -7545,7 +7602,7 @@
       <c r="C310">
         <v>1.8569</v>
       </c>
-      <c r="D310" s="4">
+      <c r="D310" s="3">
         <v>73380</v>
       </c>
       <c r="E310" s="3">
@@ -7554,7 +7611,7 @@
       <c r="F310">
         <v>99.2</v>
       </c>
-      <c r="G310" s="5">
+      <c r="G310" s="4">
         <v>6</v>
       </c>
     </row>
@@ -7568,7 +7625,7 @@
       <c r="C311">
         <v>2.1857047619999999</v>
       </c>
-      <c r="D311" s="4">
+      <c r="D311" s="3">
         <v>73350</v>
       </c>
       <c r="E311" s="3">
@@ -7577,7 +7634,7 @@
       <c r="F311">
         <v>100.1</v>
       </c>
-      <c r="G311" s="5">
+      <c r="G311" s="4">
         <v>6.2</v>
       </c>
     </row>
@@ -7591,7 +7648,7 @@
       <c r="C312">
         <v>2.8598727269999999</v>
       </c>
-      <c r="D312" s="4">
+      <c r="D312" s="3">
         <v>76177</v>
       </c>
       <c r="E312" s="3">
@@ -7600,7 +7657,7 @@
       <c r="F312">
         <v>100.2</v>
       </c>
-      <c r="G312" s="5">
+      <c r="G312" s="4">
         <v>6.6</v>
       </c>
     </row>
@@ -7614,7 +7671,7 @@
       <c r="C313">
         <v>3.1779350000000002</v>
       </c>
-      <c r="D313" s="4">
+      <c r="D313" s="3">
         <v>81795</v>
       </c>
       <c r="E313" s="3">
@@ -7623,7 +7680,7 @@
       <c r="F313">
         <v>99.7</v>
       </c>
-      <c r="G313" s="5">
+      <c r="G313" s="4">
         <v>6.2</v>
       </c>
     </row>
@@ -7637,7 +7694,7 @@
       <c r="C314">
         <v>3.427533333</v>
       </c>
-      <c r="D314" s="4">
+      <c r="D314" s="3">
         <v>75981</v>
       </c>
       <c r="E314" s="3">
@@ -7646,7 +7703,7 @@
       <c r="F314">
         <v>100.1</v>
       </c>
-      <c r="G314" s="5">
+      <c r="G314" s="4">
         <v>6.1</v>
       </c>
     </row>
@@ -7660,7 +7717,7 @@
       <c r="C315">
         <v>3.9020649999999999</v>
       </c>
-      <c r="D315" s="4">
+      <c r="D315" s="3">
         <v>74745</v>
       </c>
       <c r="E315" s="3">
@@ -7669,7 +7726,7 @@
       <c r="F315">
         <v>100.3</v>
       </c>
-      <c r="G315" s="5">
+      <c r="G315" s="4">
         <v>5.9</v>
       </c>
     </row>
@@ -7683,7 +7740,7 @@
       <c r="C316">
         <v>4.003108696</v>
       </c>
-      <c r="D316" s="4">
+      <c r="D316" s="3">
         <v>76451</v>
       </c>
       <c r="E316" s="3">
@@ -7692,7 +7749,7 @@
       <c r="F316">
         <v>99.9</v>
       </c>
-      <c r="G316" s="5">
+      <c r="G316" s="4">
         <v>6.3</v>
       </c>
     </row>
@@ -7706,7 +7763,7 @@
       <c r="C317">
         <v>4.1773611109999997</v>
       </c>
-      <c r="D317" s="4">
+      <c r="D317" s="3">
         <v>74876</v>
       </c>
       <c r="E317" s="3">
@@ -7715,7 +7772,7 @@
       <c r="F317">
         <v>100.1</v>
       </c>
-      <c r="G317" s="5">
+      <c r="G317" s="4">
         <v>6.8</v>
       </c>
     </row>
@@ -7729,7 +7786,7 @@
       <c r="C318">
         <v>4.3527800000000001</v>
       </c>
-      <c r="D318" s="4">
+      <c r="D318" s="3">
         <v>78843</v>
       </c>
       <c r="E318" s="3">
@@ -7738,7 +7795,7 @@
       <c r="F318">
         <v>99.8</v>
       </c>
-      <c r="G318" s="5">
+      <c r="G318" s="4">
         <v>7.2</v>
       </c>
     </row>
@@ -7752,7 +7809,7 @@
       <c r="C319">
         <v>4.5871863639999999</v>
       </c>
-      <c r="D319" s="4">
+      <c r="D319" s="3">
         <v>76446</v>
       </c>
       <c r="E319" s="3">
@@ -7761,7 +7818,7 @@
       <c r="F319">
         <v>100.5</v>
       </c>
-      <c r="G319" s="5">
+      <c r="G319" s="4">
         <v>8.3000000000000007</v>
       </c>
     </row>
@@ -7775,7 +7832,7 @@
       <c r="C320">
         <v>4.9302047619999998</v>
       </c>
-      <c r="D320" s="4">
+      <c r="D320" s="3">
         <v>76326</v>
       </c>
       <c r="E320" s="3">
@@ -7784,7 +7841,7 @@
       <c r="F320">
         <v>100.1</v>
       </c>
-      <c r="G320" s="5">
+      <c r="G320" s="4">
         <v>8.4</v>
       </c>
     </row>
@@ -7798,7 +7855,7 @@
       <c r="C321">
         <v>5.1609090909999997</v>
       </c>
-      <c r="D321" s="4">
+      <c r="D321" s="3">
         <v>76372</v>
       </c>
       <c r="E321" s="3">
@@ -7807,7 +7864,7 @@
       <c r="F321">
         <v>100</v>
       </c>
-      <c r="G321" s="5">
+      <c r="G321" s="4">
         <v>8.1999999999999993</v>
       </c>
     </row>
@@ -7821,7 +7878,7 @@
       <c r="C322">
         <v>5.1853857139999997</v>
       </c>
-      <c r="D322" s="4">
+      <c r="D322" s="3">
         <v>72581</v>
       </c>
       <c r="E322" s="3">
@@ -7830,7 +7887,7 @@
       <c r="F322">
         <v>100</v>
       </c>
-      <c r="G322" s="5">
+      <c r="G322" s="4">
         <v>7.8</v>
       </c>
     </row>
@@ -7844,7 +7901,7 @@
       <c r="C323">
         <v>5.1870954549999997</v>
       </c>
-      <c r="D323" s="4">
+      <c r="D323" s="3">
         <v>77793</v>
       </c>
       <c r="E323" s="3">
@@ -7853,7 +7910,7 @@
       <c r="F323">
         <v>99.6</v>
       </c>
-      <c r="G323" s="5">
+      <c r="G323" s="4">
         <v>7.1</v>
       </c>
     </row>
@@ -7867,7 +7924,7 @@
       <c r="C324">
         <v>5.1874772729999998</v>
       </c>
-      <c r="D324" s="4">
+      <c r="D324" s="3">
         <v>75837</v>
       </c>
       <c r="E324" s="3">
@@ -7876,7 +7933,7 @@
       <c r="F324">
         <v>99.9</v>
       </c>
-      <c r="G324" s="5">
+      <c r="G324" s="4">
         <v>6.6</v>
       </c>
     </row>
@@ -7890,7 +7947,7 @@
       <c r="C325">
         <v>5.1869684210000004</v>
       </c>
-      <c r="D325" s="4">
+      <c r="D325" s="3">
         <v>74168</v>
       </c>
       <c r="E325" s="3">
@@ -7899,7 +7956,7 @@
       <c r="F325">
         <v>99.6</v>
       </c>
-      <c r="G325" s="5">
+      <c r="G325" s="4">
         <v>5.8</v>
       </c>
     </row>
@@ -7913,7 +7970,7 @@
       <c r="C326">
         <v>5.1875318180000001</v>
       </c>
-      <c r="D326" s="4">
+      <c r="D326" s="3">
         <v>76080</v>
       </c>
       <c r="E326" s="3">
@@ -7922,7 +7979,7 @@
       <c r="F326">
         <v>100.1</v>
       </c>
-      <c r="G326" s="5">
+      <c r="G326" s="4">
         <v>5.7</v>
       </c>
     </row>
@@ -7936,7 +7993,7 @@
       <c r="C327">
         <v>5.1883190480000003</v>
       </c>
-      <c r="D327" s="4">
+      <c r="D327" s="3">
         <v>74597</v>
       </c>
       <c r="E327" s="3">
@@ -7945,7 +8002,7 @@
       <c r="F327">
         <v>100.3</v>
       </c>
-      <c r="G327" s="5">
+      <c r="G327" s="4">
         <v>5.7</v>
       </c>
     </row>
@@ -7959,7 +8016,7 @@
       <c r="C328">
         <v>5.1890999999999998</v>
       </c>
-      <c r="D328" s="4">
+      <c r="D328" s="3">
         <v>74826</v>
       </c>
       <c r="E328" s="3">
@@ -7968,7 +8025,7 @@
       <c r="F328">
         <v>100.8</v>
       </c>
-      <c r="G328" s="5">
+      <c r="G328" s="4">
         <v>5.9</v>
       </c>
     </row>
@@ -7982,7 +8039,7 @@
       <c r="C329">
         <v>5.1979380949999996</v>
       </c>
-      <c r="D329" s="4">
+      <c r="D329" s="3">
         <v>79680</v>
       </c>
       <c r="E329" s="3">
@@ -7991,7 +8048,7 @@
       <c r="F329">
         <v>100.8</v>
       </c>
-      <c r="G329" s="5">
+      <c r="G329" s="4">
         <v>5.8</v>
       </c>
     </row>
@@ -8005,7 +8062,7 @@
       <c r="C330">
         <v>5.2000047619999998</v>
       </c>
-      <c r="D330" s="4">
+      <c r="D330" s="3">
         <v>77007</v>
       </c>
       <c r="E330" s="3">
@@ -8014,7 +8071,7 @@
       <c r="F330">
         <v>101.2</v>
       </c>
-      <c r="G330" s="5">
+      <c r="G330" s="4">
         <v>5.8</v>
       </c>
     </row>
@@ -8028,7 +8085,7 @@
       <c r="C331">
         <v>5.2</v>
       </c>
-      <c r="D331" s="4">
+      <c r="D331" s="3">
         <v>80620</v>
       </c>
       <c r="E331" s="3">
@@ -8037,7 +8094,7 @@
       <c r="F331">
         <v>101</v>
       </c>
-      <c r="G331" s="5">
+      <c r="G331" s="4">
         <v>4.8</v>
       </c>
     </row>
@@ -8051,7 +8108,7 @@
       <c r="C332">
         <v>5.2</v>
       </c>
-      <c r="D332" s="4">
+      <c r="D332" s="3">
         <v>77104</v>
       </c>
       <c r="E332" s="3">
@@ -8060,7 +8117,7 @@
       <c r="F332">
         <v>101</v>
       </c>
-      <c r="G332" s="5">
+      <c r="G332" s="4">
         <v>4.4000000000000004</v>
       </c>
     </row>
@@ -8074,7 +8131,7 @@
       <c r="C333">
         <v>4.95</v>
       </c>
-      <c r="D333" s="4">
+      <c r="D333" s="3">
         <v>78372</v>
       </c>
       <c r="E333" s="3">
@@ -8083,7 +8140,7 @@
       <c r="F333">
         <v>101.3</v>
       </c>
-      <c r="G333" s="5">
+      <c r="G333" s="4">
         <v>4.0999999999999996</v>
       </c>
     </row>
@@ -8097,7 +8154,7 @@
       <c r="C334">
         <v>4.95</v>
       </c>
-      <c r="D334" s="4">
+      <c r="D334" s="3">
         <v>76346</v>
       </c>
       <c r="E334" s="3">
@@ -8106,7 +8163,7 @@
       <c r="F334">
         <v>101.2</v>
       </c>
-      <c r="G334" s="5">
+      <c r="G334" s="4">
         <v>4.8</v>
       </c>
     </row>
@@ -8120,7 +8177,7 @@
       <c r="C335">
         <v>4.95</v>
       </c>
-      <c r="D335" s="4">
+      <c r="D335" s="3">
         <v>80258</v>
       </c>
       <c r="E335" s="3">
@@ -8129,7 +8186,7 @@
       <c r="F335">
         <v>101.3</v>
       </c>
-      <c r="G335" s="5">
+      <c r="G335" s="4">
         <v>5.3</v>
       </c>
     </row>
@@ -8143,7 +8200,7 @@
       <c r="C336">
         <v>4.7476190479999998</v>
       </c>
-      <c r="D336" s="4">
+      <c r="D336" s="3">
         <v>80633</v>
       </c>
       <c r="E336" s="3">
@@ -8152,7 +8209,7 @@
       <c r="F336">
         <v>101.3</v>
       </c>
-      <c r="G336" s="5">
+      <c r="G336" s="4">
         <v>5.6</v>
       </c>
     </row>
@@ -8166,7 +8223,7 @@
       <c r="C337">
         <v>4.7000149999999996</v>
       </c>
-      <c r="D337" s="4">
+      <c r="D337" s="3">
         <v>79323</v>
       </c>
       <c r="E337" s="3">
@@ -8175,7 +8232,7 @@
       <c r="F337">
         <v>101.8</v>
       </c>
-      <c r="G337" s="5">
+      <c r="G337" s="4">
         <v>5.9</v>
       </c>
     </row>
@@ -8189,7 +8246,7 @@
       <c r="C338">
         <v>4.7002409089999997</v>
       </c>
-      <c r="D338" s="4">
+      <c r="D338" s="3">
         <v>78645</v>
       </c>
       <c r="E338" s="3">
@@ -8198,7 +8255,7 @@
       <c r="F338">
         <v>101.8</v>
       </c>
-      <c r="G338" s="5">
+      <c r="G338" s="4">
         <v>5.8</v>
       </c>
     </row>
@@ -8212,7 +8269,7 @@
       <c r="C339">
         <v>4.4919149999999997</v>
       </c>
-      <c r="D339" s="4">
+      <c r="D339" s="3">
         <v>81805</v>
       </c>
       <c r="E339" s="3">
@@ -8221,7 +8278,7 @@
       <c r="F339">
         <v>102.2</v>
       </c>
-      <c r="G339" s="5">
+      <c r="G339" s="4">
         <v>5.8</v>
       </c>
     </row>
@@ -8235,7 +8292,7 @@
       <c r="C340">
         <v>4.4554571430000003</v>
       </c>
-      <c r="D340" s="4">
+      <c r="D340" s="3">
         <v>82510</v>
       </c>
       <c r="E340" s="3">
@@ -8244,7 +8301,7 @@
       <c r="F340">
         <v>102.5</v>
       </c>
-      <c r="G340" s="5">
+      <c r="G340" s="4">
         <v>5.7</v>
       </c>
     </row>
@@ -8258,7 +8315,7 @@
       <c r="C341">
         <v>4.4577349999999996</v>
       </c>
-      <c r="D341" s="4">
+      <c r="D341" s="3">
         <v>80146</v>
       </c>
       <c r="E341" s="3">
@@ -8267,7 +8324,7 @@
       <c r="F341">
         <v>102.3</v>
       </c>
-      <c r="G341" s="5">
+      <c r="G341" s="4">
         <v>5.4</v>
       </c>
     </row>
@@ -8281,7 +8338,7 @@
       <c r="C342">
         <v>4.26044</v>
       </c>
-      <c r="D342" s="4">
+      <c r="D342" s="3">
         <v>81708</v>
       </c>
       <c r="E342" s="3">
@@ -8290,7 +8347,7 @@
       <c r="F342">
         <v>102.2</v>
       </c>
-      <c r="G342" s="5">
+      <c r="G342" s="4">
         <v>5</v>
       </c>
     </row>
@@ -8304,7 +8361,7 @@
       <c r="C343">
         <v>4.2144428569999999</v>
       </c>
-      <c r="D343" s="4">
+      <c r="D343" s="3">
         <v>80157</v>
       </c>
       <c r="E343" s="3">
@@ -8313,7 +8370,7 @@
       <c r="F343">
         <v>102.6</v>
       </c>
-      <c r="G343" s="5">
+      <c r="G343" s="4">
         <v>4.5999999999999996</v>
       </c>
     </row>
@@ -8327,7 +8384,7 @@
       <c r="C344">
         <v>4.217191304</v>
       </c>
-      <c r="D344" s="4">
+      <c r="D344" s="3">
         <v>81364</v>
       </c>
       <c r="E344" s="3">
@@ -8336,7 +8393,7 @@
       <c r="F344">
         <v>102.5</v>
       </c>
-      <c r="G344" s="5">
+      <c r="G344" s="4">
         <v>4.8</v>
       </c>
     </row>
@@ -8350,7 +8407,7 @@
       <c r="C345">
         <v>4.0171749999999999</v>
       </c>
-      <c r="D345" s="4">
+      <c r="D345" s="3">
         <v>80762</v>
       </c>
       <c r="E345" s="3">
@@ -8359,7 +8416,7 @@
       <c r="F345">
         <v>102.3</v>
       </c>
-      <c r="G345" s="5">
+      <c r="G345" s="4">
         <v>5</v>
       </c>
     </row>
@@ -8373,7 +8430,7 @@
       <c r="C346">
         <v>3.9671727269999999</v>
       </c>
-      <c r="D346" s="4">
+      <c r="D346" s="3">
         <v>80977</v>
       </c>
       <c r="E346" s="3">
@@ -8382,7 +8439,7 @@
       <c r="F346">
         <v>102.4</v>
       </c>
-      <c r="G346" s="5">
+      <c r="G346" s="4">
         <v>4.9000000000000004</v>
       </c>
     </row>
@@ -8396,7 +8453,7 @@
       <c r="C347">
         <v>3.9681695650000002</v>
       </c>
-      <c r="D347" s="4">
+      <c r="D347" s="3">
         <v>82649</v>
       </c>
       <c r="E347" s="3">
@@ -8405,7 +8462,7 @@
       <c r="F347">
         <v>102.3</v>
       </c>
-      <c r="G347" s="5">
+      <c r="G347" s="4">
         <v>4.8</v>
       </c>
     </row>
@@ -8419,7 +8476,7 @@
       <c r="C348">
         <v>3.9692500000000002</v>
       </c>
-      <c r="D348" s="4">
+      <c r="D348" s="3">
         <v>81993</v>
       </c>
       <c r="E348" s="3">
@@ -8428,7 +8485,7 @@
       <c r="F348">
         <v>102.5</v>
       </c>
-      <c r="G348" s="5">
+      <c r="G348" s="4">
         <v>4.5999999999999996</v>
       </c>
     </row>
@@ -8442,7 +8499,7 @@
       <c r="C349">
         <v>3.8788714290000001</v>
       </c>
-      <c r="D349" s="4">
+      <c r="D349" s="3">
         <v>80064</v>
       </c>
       <c r="E349" s="3">
@@ -8451,7 +8508,7 @@
       <c r="F349">
         <v>102.6</v>
       </c>
-      <c r="G349" s="5">
+      <c r="G349" s="4">
         <v>4.2</v>
       </c>
     </row>
@@ -8465,7 +8522,7 @@
       <c r="C350">
         <v>3.7249904759999999</v>
       </c>
-      <c r="D350" s="4">
+      <c r="D350" s="3">
         <v>79251</v>
       </c>
       <c r="E350" s="3">
@@ -8474,7 +8531,7 @@
       <c r="F350">
         <v>102.6</v>
       </c>
-      <c r="G350" s="5">
+      <c r="G350" s="4">
         <v>3.9</v>
       </c>
     </row>
@@ -8488,7 +8545,7 @@
       <c r="C351">
         <v>3.7273499999999999</v>
       </c>
-      <c r="D351" s="4">
+      <c r="D351" s="3">
         <v>81435</v>
       </c>
       <c r="E351" s="3">
@@ -8497,100 +8554,41 @@
       <c r="F351">
         <v>103</v>
       </c>
+      <c r="G351" s="8">
+        <v>3.8</v>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="K6" r:id="rId1" xr:uid="{40596D55-712E-447C-A43A-8D78FF9FCFB8}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38B3F947-54D3-45E9-960A-0A3480DB2752}">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="35.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
     <col min="3" max="3" width="18.5546875" customWidth="1"/>
   </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" s="1">
-        <v>46054</v>
-      </c>
-      <c r="E4" s="8">
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="1">
-        <v>46082</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="1">
-        <v>46023</v>
-      </c>
-      <c r="E6" s="8">
-        <v>46133</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" s="1">
-        <v>46054</v>
-      </c>
-      <c r="E7" s="7">
-        <v>46130</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" t="s">
-        <v>14</v>
-      </c>
-      <c r="D8" s="1">
-        <v>46054</v>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="C4" r:id="rId1" xr:uid="{40596D55-712E-447C-A43A-8D78FF9FCFB8}"/>
-  </hyperlinks>
+  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="d3fc78fc-ba6f-4a58-b9ca-9976000a3bf3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101003C274FC0B9B90A47AC72E41740964DE2" ma:contentTypeVersion="10" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="dc92802ba148964756caf43e1d0d29c8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="d3fc78fc-ba6f-4a58-b9ca-9976000a3bf3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1a094c132005110b8da62a9dd3dd1317" ns3:_="">
     <xsd:import namespace="d3fc78fc-ba6f-4a58-b9ca-9976000a3bf3"/>
@@ -8770,7 +8768,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -8779,15 +8777,23 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="d3fc78fc-ba6f-4a58-b9ca-9976000a3bf3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{312375B1-C16D-4AB5-AD8B-C0F1708B1636}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="d3fc78fc-ba6f-4a58-b9ca-9976000a3bf3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9CC83991-D924-4F98-9DFE-5E0BA4637408}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8805,26 +8811,10 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5BC7D0FC-CEB7-44BF-98D3-20B16875BB18}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{312375B1-C16D-4AB5-AD8B-C0F1708B1636}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="d3fc78fc-ba6f-4a58-b9ca-9976000a3bf3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>